--- a/public/tests/data/test_simple.xlsx
+++ b/public/tests/data/test_simple.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECB7C1CC-F8A8-444B-A7B6-3A5FCD194F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62ABAE93-5FFD-4AFB-A6AF-6BC0C4197D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="main" sheetId="1" r:id="rId1"/>
+    <sheet name="Main" sheetId="1" r:id="rId1"/>
     <sheet name="Portfolios" sheetId="2" r:id="rId2"/>
     <sheet name="Assets" sheetId="4" r:id="rId3"/>
   </sheets>

--- a/public/tests/data/test_simple.xlsx
+++ b/public/tests/data/test_simple.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62ABAE93-5FFD-4AFB-A6AF-6BC0C4197D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C65D32-5A26-4B92-879B-9D05E524C5AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
     <sheet name="Portfolios" sheetId="2" r:id="rId2"/>
     <sheet name="Assets" sheetId="4" r:id="rId3"/>
+    <sheet name="Prices" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
   <si>
     <t>Name</t>
   </si>
@@ -78,6 +79,15 @@
   </si>
   <si>
     <t>Port2</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>Proxy</t>
+  </si>
+  <si>
+    <t>Date</t>
   </si>
 </sst>
 </file>
@@ -508,34 +518,422 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C271D88-DDEC-4A65-8905-A99CA73725FC}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="14.921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1942483-BB80-4E18-92F0-22F7848078C4}">
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="10.07421875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" s="2">
+        <v>45658</v>
+      </c>
+      <c r="B2">
+        <v>100</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="2">
+        <v>45659</v>
+      </c>
+      <c r="B3">
+        <v>101</v>
+      </c>
+      <c r="C3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" s="2">
+        <v>45660</v>
+      </c>
+      <c r="B4">
+        <v>102</v>
+      </c>
+      <c r="C4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" s="2">
+        <v>45661</v>
+      </c>
+      <c r="B5">
+        <v>103</v>
+      </c>
+      <c r="C5">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" s="2">
+        <v>45662</v>
+      </c>
+      <c r="B6">
+        <v>104</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" s="2">
+        <v>45663</v>
+      </c>
+      <c r="B7">
+        <v>105</v>
+      </c>
+      <c r="C7">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" s="2">
+        <v>45664</v>
+      </c>
+      <c r="B8">
+        <v>106</v>
+      </c>
+      <c r="C8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" s="2">
+        <v>45665</v>
+      </c>
+      <c r="B9">
+        <v>107</v>
+      </c>
+      <c r="C9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" s="2">
+        <v>45666</v>
+      </c>
+      <c r="B10">
+        <v>108</v>
+      </c>
+      <c r="C10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A11" s="2">
+        <v>45667</v>
+      </c>
+      <c r="B11">
+        <v>109</v>
+      </c>
+      <c r="C11">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A12" s="2">
+        <v>45668</v>
+      </c>
+      <c r="B12">
+        <v>110</v>
+      </c>
+      <c r="C12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A13" s="2">
+        <v>45669</v>
+      </c>
+      <c r="B13">
+        <v>111</v>
+      </c>
+      <c r="C13">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A14" s="2">
+        <v>45670</v>
+      </c>
+      <c r="B14">
+        <v>112</v>
+      </c>
+      <c r="C14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A15" s="2">
+        <v>45671</v>
+      </c>
+      <c r="B15">
+        <v>113</v>
+      </c>
+      <c r="C15">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A16" s="2">
+        <v>45672</v>
+      </c>
+      <c r="B16">
+        <v>114</v>
+      </c>
+      <c r="C16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A17" s="2">
+        <v>45673</v>
+      </c>
+      <c r="B17">
+        <v>115</v>
+      </c>
+      <c r="C17">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A18" s="2">
+        <v>45674</v>
+      </c>
+      <c r="B18">
+        <v>116</v>
+      </c>
+      <c r="C18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A19" s="2">
+        <v>45675</v>
+      </c>
+      <c r="B19">
+        <v>117</v>
+      </c>
+      <c r="C19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A20" s="2">
+        <v>45676</v>
+      </c>
+      <c r="B20">
+        <v>118</v>
+      </c>
+      <c r="C20">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A21" s="2">
+        <v>45677</v>
+      </c>
+      <c r="B21">
+        <v>119</v>
+      </c>
+      <c r="C21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A22" s="2">
+        <v>45678</v>
+      </c>
+      <c r="B22">
+        <v>120</v>
+      </c>
+      <c r="C22">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A23" s="2">
+        <v>45679</v>
+      </c>
+      <c r="B23">
+        <v>121</v>
+      </c>
+      <c r="C23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A24" s="2">
+        <v>45680</v>
+      </c>
+      <c r="B24">
+        <v>122</v>
+      </c>
+      <c r="C24">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A25" s="2">
+        <v>45681</v>
+      </c>
+      <c r="B25">
+        <v>123</v>
+      </c>
+      <c r="C25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A26" s="2">
+        <v>45682</v>
+      </c>
+      <c r="B26">
+        <v>124</v>
+      </c>
+      <c r="C26">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A27" s="2">
+        <v>45683</v>
+      </c>
+      <c r="B27">
+        <v>125</v>
+      </c>
+      <c r="C27">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A28" s="2">
+        <v>45684</v>
+      </c>
+      <c r="B28">
+        <v>126</v>
+      </c>
+      <c r="C28">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A29" s="2">
+        <v>45685</v>
+      </c>
+      <c r="B29">
+        <v>127</v>
+      </c>
+      <c r="C29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A30" s="2">
+        <v>45686</v>
+      </c>
+      <c r="B30">
+        <v>128</v>
+      </c>
+      <c r="C30">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A31" s="2">
+        <v>45687</v>
+      </c>
+      <c r="B31">
+        <v>129</v>
+      </c>
+      <c r="C31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A32" s="2">
+        <v>45688</v>
+      </c>
+      <c r="B32">
+        <v>130</v>
+      </c>
+      <c r="C32">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A33" s="2">
+        <v>45689</v>
+      </c>
+      <c r="B33">
+        <v>131</v>
+      </c>
+      <c r="C33">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/public/tests/data/test_simple.xlsx
+++ b/public/tests/data/test_simple.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C65D32-5A26-4B92-879B-9D05E524C5AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B59B07-F883-43DF-9231-B2526336F83D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
     <sheet name="Portfolios" sheetId="2" r:id="rId2"/>
     <sheet name="Assets" sheetId="4" r:id="rId3"/>
     <sheet name="Prices" sheetId="5" r:id="rId4"/>
+    <sheet name="Expected_Portfolio_Values" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
   <si>
     <t>Name</t>
   </si>
@@ -75,12 +76,6 @@
     <t>Portfolios</t>
   </si>
   <si>
-    <t>Port1</t>
-  </si>
-  <si>
-    <t>Port2</t>
-  </si>
-  <si>
     <t>Currency</t>
   </si>
   <si>
@@ -88,6 +83,12 @@
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>P2</t>
   </si>
 </sst>
 </file>
@@ -131,11 +132,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -486,10 +489,10 @@
         <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
@@ -497,9 +500,6 @@
         <v>10</v>
       </c>
       <c r="B2" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="C2" s="3">
         <v>1</v>
       </c>
     </row>
@@ -507,8 +507,9 @@
       <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3">
-        <v>0.5</v>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -532,10 +533,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
@@ -575,7 +576,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>10</v>
@@ -779,7 +780,7 @@
         <v>117</v>
       </c>
       <c r="C19">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.4">
@@ -790,7 +791,7 @@
         <v>118</v>
       </c>
       <c r="C20">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
@@ -801,7 +802,7 @@
         <v>119</v>
       </c>
       <c r="C21">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
@@ -812,7 +813,7 @@
         <v>120</v>
       </c>
       <c r="C22">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.4">
@@ -823,7 +824,7 @@
         <v>121</v>
       </c>
       <c r="C23">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.4">
@@ -834,7 +835,7 @@
         <v>122</v>
       </c>
       <c r="C24">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.4">
@@ -845,7 +846,7 @@
         <v>123</v>
       </c>
       <c r="C25">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.4">
@@ -856,7 +857,7 @@
         <v>124</v>
       </c>
       <c r="C26">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">
@@ -867,7 +868,7 @@
         <v>125</v>
       </c>
       <c r="C27">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.4">
@@ -878,7 +879,7 @@
         <v>126</v>
       </c>
       <c r="C28">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.4">
@@ -889,7 +890,7 @@
         <v>127</v>
       </c>
       <c r="C29">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.4">
@@ -900,7 +901,7 @@
         <v>128</v>
       </c>
       <c r="C30">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.4">
@@ -911,7 +912,7 @@
         <v>129</v>
       </c>
       <c r="C31">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.4">
@@ -922,7 +923,7 @@
         <v>130</v>
       </c>
       <c r="C32">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.4">
@@ -933,8 +934,397 @@
         <v>131</v>
       </c>
       <c r="C33">
-        <v>100</v>
-      </c>
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B9E8070-11EC-4D5B-882F-63D06BDC939E}">
+  <dimension ref="A1:C37"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="10.07421875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.23046875" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" s="2">
+        <v>45658</v>
+      </c>
+      <c r="B2" s="5">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="2">
+        <v>45659</v>
+      </c>
+      <c r="B3" s="5">
+        <v>1.01</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" s="2">
+        <v>45660</v>
+      </c>
+      <c r="B4" s="5">
+        <v>1.02</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" s="2">
+        <v>45661</v>
+      </c>
+      <c r="B5" s="5">
+        <v>1.03</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" s="2">
+        <v>45662</v>
+      </c>
+      <c r="B6" s="5">
+        <v>1.04</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" s="2">
+        <v>45663</v>
+      </c>
+      <c r="B7" s="5">
+        <v>1.05</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" s="2">
+        <v>45664</v>
+      </c>
+      <c r="B8" s="5">
+        <v>1.06</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" s="2">
+        <v>45665</v>
+      </c>
+      <c r="B9" s="5">
+        <v>1.07</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" s="2">
+        <v>45666</v>
+      </c>
+      <c r="B10" s="5">
+        <v>1.08</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A11" s="2">
+        <v>45667</v>
+      </c>
+      <c r="B11" s="5">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A12" s="2">
+        <v>45668</v>
+      </c>
+      <c r="B12" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A13" s="2">
+        <v>45669</v>
+      </c>
+      <c r="B13" s="5">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A14" s="2">
+        <v>45670</v>
+      </c>
+      <c r="B14" s="5">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A15" s="2">
+        <v>45671</v>
+      </c>
+      <c r="B15" s="5">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A16" s="2">
+        <v>45672</v>
+      </c>
+      <c r="B16" s="5">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A17" s="2">
+        <v>45673</v>
+      </c>
+      <c r="B17" s="5">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A18" s="2">
+        <v>45674</v>
+      </c>
+      <c r="B18" s="5">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="C18" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A19" s="2">
+        <v>45675</v>
+      </c>
+      <c r="B19" s="5">
+        <v>1.17</v>
+      </c>
+      <c r="C19" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A20" s="2">
+        <v>45676</v>
+      </c>
+      <c r="B20" s="5">
+        <v>1.18</v>
+      </c>
+      <c r="C20" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A21" s="2">
+        <v>45677</v>
+      </c>
+      <c r="B21" s="5">
+        <v>1.19</v>
+      </c>
+      <c r="C21" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A22" s="2">
+        <v>45678</v>
+      </c>
+      <c r="B22" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A23" s="2">
+        <v>45679</v>
+      </c>
+      <c r="B23" s="5">
+        <v>1.21</v>
+      </c>
+      <c r="C23" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A24" s="2">
+        <v>45680</v>
+      </c>
+      <c r="B24" s="5">
+        <v>1.22</v>
+      </c>
+      <c r="C24" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A25" s="2">
+        <v>45681</v>
+      </c>
+      <c r="B25" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="C25" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A26" s="2">
+        <v>45682</v>
+      </c>
+      <c r="B26" s="5">
+        <v>1.24</v>
+      </c>
+      <c r="C26" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A27" s="2">
+        <v>45683</v>
+      </c>
+      <c r="B27" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="C27" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A28" s="2">
+        <v>45684</v>
+      </c>
+      <c r="B28" s="5">
+        <v>1.26</v>
+      </c>
+      <c r="C28" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A29" s="2">
+        <v>45685</v>
+      </c>
+      <c r="B29" s="5">
+        <v>1.27</v>
+      </c>
+      <c r="C29" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A30" s="2">
+        <v>45686</v>
+      </c>
+      <c r="B30" s="5">
+        <v>1.28</v>
+      </c>
+      <c r="C30" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A31" s="2">
+        <v>45687</v>
+      </c>
+      <c r="B31" s="5">
+        <v>1.29</v>
+      </c>
+      <c r="C31" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A32" s="2">
+        <v>45688</v>
+      </c>
+      <c r="B32" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="C32" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A33" s="2">
+        <v>45689</v>
+      </c>
+      <c r="B33" s="5">
+        <v>1.31</v>
+      </c>
+      <c r="C33" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C34" s="5"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C35" s="5"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C36" s="5"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C37" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/tests/data/test_simple.xlsx
+++ b/public/tests/data/test_simple.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B59B07-F883-43DF-9231-B2526336F83D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8207CCD2-FFA7-469A-9E6A-F38C90C589F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,7 @@
     <sheet name="Assets" sheetId="4" r:id="rId3"/>
     <sheet name="Prices" sheetId="5" r:id="rId4"/>
     <sheet name="Expected_Portfolio_Values" sheetId="6" r:id="rId5"/>
+    <sheet name="Expected_Portfolio_Weights" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="25">
   <si>
     <t>Name</t>
   </si>
@@ -89,13 +90,28 @@
   </si>
   <si>
     <t>P2</t>
+  </si>
+  <si>
+    <t>P1&gt;A1</t>
+  </si>
+  <si>
+    <t>P2&gt;A2</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>P3&gt;A1</t>
+  </si>
+  <si>
+    <t>P3&gt;A2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,6 +121,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -129,19 +152,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -481,10 +507,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{955DA01E-A3C8-43F7-BE2B-2D20BB66CB4A}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -494,22 +520,31 @@
       <c r="C1" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D2" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3">
         <v>1</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -944,14 +979,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B9E8070-11EC-4D5B-882F-63D06BDC939E}">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.07421875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.23046875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -961,8 +996,11 @@
       <c r="C1" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>45658</v>
       </c>
@@ -972,8 +1010,11 @@
       <c r="C2" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D2" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>45659</v>
       </c>
@@ -983,8 +1024,11 @@
       <c r="C3" s="5">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D3" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>45660</v>
       </c>
@@ -994,8 +1038,11 @@
       <c r="C4" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>45661</v>
       </c>
@@ -1005,8 +1052,11 @@
       <c r="C5" s="5">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D5" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>45662</v>
       </c>
@@ -1016,8 +1066,11 @@
       <c r="C6" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>45663</v>
       </c>
@@ -1027,8 +1080,11 @@
       <c r="C7" s="5">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D7" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>45664</v>
       </c>
@@ -1038,8 +1094,11 @@
       <c r="C8" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>45665</v>
       </c>
@@ -1049,8 +1108,11 @@
       <c r="C9" s="5">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D9" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>45666</v>
       </c>
@@ -1060,8 +1122,11 @@
       <c r="C10" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D10" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>45667</v>
       </c>
@@ -1071,8 +1136,11 @@
       <c r="C11" s="5">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D11" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>45668</v>
       </c>
@@ -1082,8 +1150,11 @@
       <c r="C12" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D12" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>45669</v>
       </c>
@@ -1093,8 +1164,11 @@
       <c r="C13" s="5">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D13" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>45670</v>
       </c>
@@ -1104,8 +1178,11 @@
       <c r="C14" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D14" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>45671</v>
       </c>
@@ -1115,8 +1192,11 @@
       <c r="C15" s="5">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D15" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>45672</v>
       </c>
@@ -1126,8 +1206,11 @@
       <c r="C16" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D16" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>45673</v>
       </c>
@@ -1137,8 +1220,11 @@
       <c r="C17" s="5">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D17" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>45674</v>
       </c>
@@ -1148,8 +1234,11 @@
       <c r="C18" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D18" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>45675</v>
       </c>
@@ -1159,8 +1248,11 @@
       <c r="C19" s="5">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D19" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>45676</v>
       </c>
@@ -1170,8 +1262,11 @@
       <c r="C20" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D20" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>45677</v>
       </c>
@@ -1181,8 +1276,11 @@
       <c r="C21" s="5">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D21" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>45678</v>
       </c>
@@ -1192,8 +1290,11 @@
       <c r="C22" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D22" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>45679</v>
       </c>
@@ -1203,8 +1304,11 @@
       <c r="C23" s="5">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D23" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>45680</v>
       </c>
@@ -1214,8 +1318,11 @@
       <c r="C24" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D24" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>45681</v>
       </c>
@@ -1225,8 +1332,11 @@
       <c r="C25" s="5">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D25" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>45682</v>
       </c>
@@ -1236,8 +1346,11 @@
       <c r="C26" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D26" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>45683</v>
       </c>
@@ -1247,8 +1360,11 @@
       <c r="C27" s="5">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D27" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>45684</v>
       </c>
@@ -1258,8 +1374,11 @@
       <c r="C28" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D28" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>45685</v>
       </c>
@@ -1269,8 +1388,11 @@
       <c r="C29" s="5">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D29" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>45686</v>
       </c>
@@ -1280,8 +1402,11 @@
       <c r="C30" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D30" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>45687</v>
       </c>
@@ -1291,8 +1416,11 @@
       <c r="C31" s="5">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D31" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>45688</v>
       </c>
@@ -1302,8 +1430,11 @@
       <c r="C32" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D32" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <v>45689</v>
       </c>
@@ -1313,18 +1444,595 @@
       <c r="C33" s="5">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D33" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C34" s="5"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C35" s="5"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C36" s="5"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C37" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93EA1201-9593-4FA8-BE4A-D6543E3F5A5B}">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="10.07421875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A2" s="2">
+        <v>45658</v>
+      </c>
+      <c r="B2" s="6">
+        <v>1</v>
+      </c>
+      <c r="C2" s="6">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A3" s="2">
+        <v>45659</v>
+      </c>
+      <c r="B3" s="6">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" s="2">
+        <v>45660</v>
+      </c>
+      <c r="B4" s="6">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A5" s="2">
+        <v>45661</v>
+      </c>
+      <c r="B5" s="6">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A6" s="2">
+        <v>45662</v>
+      </c>
+      <c r="B6" s="6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A7" s="2">
+        <v>45663</v>
+      </c>
+      <c r="B7" s="6">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A8" s="2">
+        <v>45664</v>
+      </c>
+      <c r="B8" s="6">
+        <v>1</v>
+      </c>
+      <c r="C8" s="6">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A9" s="2">
+        <v>45665</v>
+      </c>
+      <c r="B9" s="6">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A10" s="2">
+        <v>45666</v>
+      </c>
+      <c r="B10" s="6">
+        <v>1</v>
+      </c>
+      <c r="C10" s="6">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A11" s="2">
+        <v>45667</v>
+      </c>
+      <c r="B11" s="6">
+        <v>1</v>
+      </c>
+      <c r="C11" s="6">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A12" s="2">
+        <v>45668</v>
+      </c>
+      <c r="B12" s="6">
+        <v>1</v>
+      </c>
+      <c r="C12" s="6">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A13" s="2">
+        <v>45669</v>
+      </c>
+      <c r="B13" s="6">
+        <v>1</v>
+      </c>
+      <c r="C13" s="6">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A14" s="2">
+        <v>45670</v>
+      </c>
+      <c r="B14" s="6">
+        <v>1</v>
+      </c>
+      <c r="C14" s="6">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A15" s="2">
+        <v>45671</v>
+      </c>
+      <c r="B15" s="6">
+        <v>1</v>
+      </c>
+      <c r="C15" s="6">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A16" s="2">
+        <v>45672</v>
+      </c>
+      <c r="B16" s="6">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A17" s="2">
+        <v>45673</v>
+      </c>
+      <c r="B17" s="6">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A18" s="2">
+        <v>45674</v>
+      </c>
+      <c r="B18" s="6">
+        <v>1</v>
+      </c>
+      <c r="C18" s="6">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A19" s="2">
+        <v>45675</v>
+      </c>
+      <c r="B19" s="6">
+        <v>1</v>
+      </c>
+      <c r="C19" s="6">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A20" s="2">
+        <v>45676</v>
+      </c>
+      <c r="B20" s="6">
+        <v>1</v>
+      </c>
+      <c r="C20" s="6">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A21" s="2">
+        <v>45677</v>
+      </c>
+      <c r="B21" s="6">
+        <v>1</v>
+      </c>
+      <c r="C21" s="6">
+        <v>1</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A22" s="2">
+        <v>45678</v>
+      </c>
+      <c r="B22" s="6">
+        <v>1</v>
+      </c>
+      <c r="C22" s="6">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A23" s="2">
+        <v>45679</v>
+      </c>
+      <c r="B23" s="6">
+        <v>1</v>
+      </c>
+      <c r="C23" s="6">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A24" s="2">
+        <v>45680</v>
+      </c>
+      <c r="B24" s="6">
+        <v>1</v>
+      </c>
+      <c r="C24" s="6">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A25" s="2">
+        <v>45681</v>
+      </c>
+      <c r="B25" s="6">
+        <v>1</v>
+      </c>
+      <c r="C25" s="6">
+        <v>1</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A26" s="2">
+        <v>45682</v>
+      </c>
+      <c r="B26" s="6">
+        <v>1</v>
+      </c>
+      <c r="C26" s="6">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A27" s="2">
+        <v>45683</v>
+      </c>
+      <c r="B27" s="6">
+        <v>1</v>
+      </c>
+      <c r="C27" s="6">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A28" s="2">
+        <v>45684</v>
+      </c>
+      <c r="B28" s="6">
+        <v>1</v>
+      </c>
+      <c r="C28" s="6">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E28" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A29" s="2">
+        <v>45685</v>
+      </c>
+      <c r="B29" s="6">
+        <v>1</v>
+      </c>
+      <c r="C29" s="6">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A30" s="2">
+        <v>45686</v>
+      </c>
+      <c r="B30" s="6">
+        <v>1</v>
+      </c>
+      <c r="C30" s="6">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E30" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A31" s="2">
+        <v>45687</v>
+      </c>
+      <c r="B31" s="6">
+        <v>1</v>
+      </c>
+      <c r="C31" s="6">
+        <v>1</v>
+      </c>
+      <c r="D31" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E31" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A32" s="2">
+        <v>45688</v>
+      </c>
+      <c r="B32" s="6">
+        <v>1</v>
+      </c>
+      <c r="C32" s="6">
+        <v>1</v>
+      </c>
+      <c r="D32" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A33" s="2">
+        <v>45689</v>
+      </c>
+      <c r="B33" s="6">
+        <v>1</v>
+      </c>
+      <c r="C33" s="6">
+        <v>1</v>
+      </c>
+      <c r="D33" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0.5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/tests/data/test_simple.xlsx
+++ b/public/tests/data/test_simple.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8207CCD2-FFA7-469A-9E6A-F38C90C589F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F3DBB8-674F-4138-BAF5-58109BF08BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,6 +19,7 @@
     <sheet name="Prices" sheetId="5" r:id="rId4"/>
     <sheet name="Expected_Portfolio_Values" sheetId="6" r:id="rId5"/>
     <sheet name="Expected_Portfolio_Weights" sheetId="7" r:id="rId6"/>
+    <sheet name="Sheet5" sheetId="9" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
   <si>
     <t>Name</t>
   </si>
@@ -105,12 +106,18 @@
   </si>
   <si>
     <t>P3&gt;A2</t>
+  </si>
+  <si>
+    <t>Portfolio Value</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="169" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -156,14 +163,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -979,24 +987,24 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B9E8070-11EC-4D5B-882F-63D06BDC939E}">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.07421875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.23046875" style="5"/>
+    <col min="2" max="4" width="9.23046875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1004,13 +1012,13 @@
       <c r="A2" s="2">
         <v>45658</v>
       </c>
-      <c r="B2" s="5">
-        <v>1</v>
-      </c>
-      <c r="C2" s="5">
-        <v>1</v>
-      </c>
-      <c r="D2" s="5">
+      <c r="B2" s="7">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7">
+        <v>1</v>
+      </c>
+      <c r="D2" s="7">
         <v>1</v>
       </c>
     </row>
@@ -1018,447 +1026,435 @@
       <c r="A3" s="2">
         <v>45659</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="7">
         <v>1.01</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="7">
         <v>0.9</v>
       </c>
-      <c r="D3" s="5">
-        <v>0.9</v>
+      <c r="D3" s="7">
+        <v>0.95499999999999996</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>45660</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="7">
         <v>1.02</v>
       </c>
-      <c r="C4" s="5">
-        <v>1</v>
-      </c>
-      <c r="D4" s="5">
-        <v>1</v>
+      <c r="C4" s="7">
+        <v>1</v>
+      </c>
+      <c r="D4" s="7">
+        <v>1.01</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>45661</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="7">
         <v>1.03</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="7">
         <v>0.9</v>
       </c>
-      <c r="D5" s="5">
-        <v>0.9</v>
+      <c r="D5" s="7">
+        <v>0.96499999999999997</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>45662</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="7">
         <v>1.04</v>
       </c>
-      <c r="C6" s="5">
-        <v>1</v>
-      </c>
-      <c r="D6" s="5">
-        <v>1</v>
+      <c r="C6" s="7">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7">
+        <v>1.02</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>45663</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="7">
         <v>1.05</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="7">
         <v>0.9</v>
       </c>
-      <c r="D7" s="5">
-        <v>0.9</v>
+      <c r="D7" s="7">
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>45664</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="7">
         <v>1.06</v>
       </c>
-      <c r="C8" s="5">
-        <v>1</v>
-      </c>
-      <c r="D8" s="5">
-        <v>1</v>
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7">
+        <v>1.03</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>45665</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="7">
         <v>1.07</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="7">
         <v>0.9</v>
       </c>
-      <c r="D9" s="5">
-        <v>0.9</v>
+      <c r="D9" s="7">
+        <v>0.98499999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>45666</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="7">
         <v>1.08</v>
       </c>
-      <c r="C10" s="5">
-        <v>1</v>
-      </c>
-      <c r="D10" s="5">
-        <v>1</v>
+      <c r="C10" s="7">
+        <v>1</v>
+      </c>
+      <c r="D10" s="7">
+        <v>1.04</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>45667</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="7">
         <v>1.0900000000000001</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="7">
         <v>0.9</v>
       </c>
-      <c r="D11" s="5">
-        <v>0.9</v>
+      <c r="D11" s="7">
+        <v>0.995</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>45668</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="7">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C12" s="5">
-        <v>1</v>
-      </c>
-      <c r="D12" s="5">
-        <v>1</v>
+      <c r="C12" s="7">
+        <v>1</v>
+      </c>
+      <c r="D12" s="7">
+        <v>1.05</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>45669</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="7">
         <v>1.1100000000000001</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="7">
         <v>0.9</v>
       </c>
-      <c r="D13" s="5">
-        <v>0.9</v>
+      <c r="D13" s="7">
+        <v>1.0049999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>45670</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="7">
         <v>1.1200000000000001</v>
       </c>
-      <c r="C14" s="5">
-        <v>1</v>
-      </c>
-      <c r="D14" s="5">
-        <v>1</v>
+      <c r="C14" s="7">
+        <v>1</v>
+      </c>
+      <c r="D14" s="7">
+        <v>1.06</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>45671</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="7">
         <v>1.1299999999999999</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="7">
         <v>0.9</v>
       </c>
-      <c r="D15" s="5">
-        <v>0.9</v>
+      <c r="D15" s="7">
+        <v>1.0149999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>45672</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="7">
         <v>1.1399999999999999</v>
       </c>
-      <c r="C16" s="5">
-        <v>1</v>
-      </c>
-      <c r="D16" s="5">
-        <v>1</v>
+      <c r="C16" s="7">
+        <v>1</v>
+      </c>
+      <c r="D16" s="7">
+        <v>1.07</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>45673</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="7">
         <v>1.1499999999999999</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="7">
         <v>0.9</v>
       </c>
-      <c r="D17" s="5">
-        <v>0.9</v>
+      <c r="D17" s="7">
+        <v>1.0249999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>45674</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="7">
         <v>1.1599999999999999</v>
       </c>
-      <c r="C18" s="5">
-        <v>1</v>
-      </c>
-      <c r="D18" s="5">
-        <v>1</v>
+      <c r="C18" s="7">
+        <v>1</v>
+      </c>
+      <c r="D18" s="7">
+        <v>1.08</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>45675</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="7">
         <v>1.17</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="7">
         <v>0.9</v>
       </c>
-      <c r="D19" s="5">
-        <v>0.9</v>
+      <c r="D19" s="7">
+        <v>1.0349999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>45676</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="7">
         <v>1.18</v>
       </c>
-      <c r="C20" s="5">
-        <v>1</v>
-      </c>
-      <c r="D20" s="5">
-        <v>1</v>
+      <c r="C20" s="7">
+        <v>1</v>
+      </c>
+      <c r="D20" s="7">
+        <v>1.0900000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>45677</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="7">
         <v>1.19</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="7">
         <v>0.9</v>
       </c>
-      <c r="D21" s="5">
-        <v>0.9</v>
+      <c r="D21" s="7">
+        <v>1.0449999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>45678</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="7">
         <v>1.2</v>
       </c>
-      <c r="C22" s="5">
-        <v>1</v>
-      </c>
-      <c r="D22" s="5">
-        <v>1</v>
+      <c r="C22" s="7">
+        <v>1</v>
+      </c>
+      <c r="D22" s="7">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>45679</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="7">
         <v>1.21</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="7">
         <v>0.9</v>
       </c>
-      <c r="D23" s="5">
-        <v>0.9</v>
+      <c r="D23" s="7">
+        <v>1.0549999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>45680</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="7">
         <v>1.22</v>
       </c>
-      <c r="C24" s="5">
-        <v>1</v>
-      </c>
-      <c r="D24" s="5">
-        <v>1</v>
+      <c r="C24" s="7">
+        <v>1</v>
+      </c>
+      <c r="D24" s="7">
+        <v>1.1100000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>45681</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="7">
         <v>1.23</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="7">
         <v>0.9</v>
       </c>
-      <c r="D25" s="5">
-        <v>0.9</v>
+      <c r="D25" s="7">
+        <v>1.0649999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>45682</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26" s="7">
         <v>1.24</v>
       </c>
-      <c r="C26" s="5">
-        <v>1</v>
-      </c>
-      <c r="D26" s="5">
-        <v>1</v>
+      <c r="C26" s="7">
+        <v>1</v>
+      </c>
+      <c r="D26" s="7">
+        <v>1.1200000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>45683</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="7">
         <v>1.25</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="7">
         <v>0.9</v>
       </c>
-      <c r="D27" s="5">
-        <v>0.9</v>
+      <c r="D27" s="7">
+        <v>1.075</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>45684</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="7">
         <v>1.26</v>
       </c>
-      <c r="C28" s="5">
-        <v>1</v>
-      </c>
-      <c r="D28" s="5">
-        <v>1</v>
+      <c r="C28" s="7">
+        <v>1</v>
+      </c>
+      <c r="D28" s="7">
+        <v>1.1299999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>45685</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="7">
         <v>1.27</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29" s="7">
         <v>0.9</v>
       </c>
-      <c r="D29" s="5">
-        <v>0.9</v>
+      <c r="D29" s="7">
+        <v>1.085</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>45686</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="7">
         <v>1.28</v>
       </c>
-      <c r="C30" s="5">
-        <v>1</v>
-      </c>
-      <c r="D30" s="5">
-        <v>1</v>
+      <c r="C30" s="7">
+        <v>1</v>
+      </c>
+      <c r="D30" s="7">
+        <v>1.1399999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>45687</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31" s="7">
         <v>1.29</v>
       </c>
-      <c r="C31" s="5">
+      <c r="C31" s="7">
         <v>0.9</v>
       </c>
-      <c r="D31" s="5">
-        <v>0.9</v>
+      <c r="D31" s="7">
+        <v>1.095</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>45688</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32" s="7">
         <v>1.3</v>
       </c>
-      <c r="C32" s="5">
-        <v>1</v>
-      </c>
-      <c r="D32" s="5">
-        <v>1</v>
+      <c r="C32" s="7">
+        <v>1</v>
+      </c>
+      <c r="D32" s="7">
+        <v>1.1499999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <v>45689</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33" s="7">
         <v>1.31</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C33" s="7">
         <v>0.9</v>
       </c>
-      <c r="D33" s="5">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C34" s="5"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C35" s="5"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C36" s="5"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C37" s="5"/>
+      <c r="D33" s="7">
+        <v>1.105</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1494,10 +1490,10 @@
       <c r="A2" s="2">
         <v>45658</v>
       </c>
-      <c r="B2" s="6">
-        <v>1</v>
-      </c>
-      <c r="C2" s="6">
+      <c r="B2" s="5">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5">
         <v>1</v>
       </c>
       <c r="D2" s="3">
@@ -1511,10 +1507,10 @@
       <c r="A3" s="2">
         <v>45659</v>
       </c>
-      <c r="B3" s="6">
-        <v>1</v>
-      </c>
-      <c r="C3" s="6">
+      <c r="B3" s="5">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5">
         <v>1</v>
       </c>
       <c r="D3" s="3">
@@ -1528,10 +1524,10 @@
       <c r="A4" s="2">
         <v>45660</v>
       </c>
-      <c r="B4" s="6">
-        <v>1</v>
-      </c>
-      <c r="C4" s="6">
+      <c r="B4" s="5">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5">
         <v>1</v>
       </c>
       <c r="D4" s="3">
@@ -1545,10 +1541,10 @@
       <c r="A5" s="2">
         <v>45661</v>
       </c>
-      <c r="B5" s="6">
-        <v>1</v>
-      </c>
-      <c r="C5" s="6">
+      <c r="B5" s="5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5">
         <v>1</v>
       </c>
       <c r="D5" s="3">
@@ -1562,10 +1558,10 @@
       <c r="A6" s="2">
         <v>45662</v>
       </c>
-      <c r="B6" s="6">
-        <v>1</v>
-      </c>
-      <c r="C6" s="6">
+      <c r="B6" s="5">
+        <v>1</v>
+      </c>
+      <c r="C6" s="5">
         <v>1</v>
       </c>
       <c r="D6" s="3">
@@ -1579,10 +1575,10 @@
       <c r="A7" s="2">
         <v>45663</v>
       </c>
-      <c r="B7" s="6">
-        <v>1</v>
-      </c>
-      <c r="C7" s="6">
+      <c r="B7" s="5">
+        <v>1</v>
+      </c>
+      <c r="C7" s="5">
         <v>1</v>
       </c>
       <c r="D7" s="3">
@@ -1596,10 +1592,10 @@
       <c r="A8" s="2">
         <v>45664</v>
       </c>
-      <c r="B8" s="6">
-        <v>1</v>
-      </c>
-      <c r="C8" s="6">
+      <c r="B8" s="5">
+        <v>1</v>
+      </c>
+      <c r="C8" s="5">
         <v>1</v>
       </c>
       <c r="D8" s="3">
@@ -1613,10 +1609,10 @@
       <c r="A9" s="2">
         <v>45665</v>
       </c>
-      <c r="B9" s="6">
-        <v>1</v>
-      </c>
-      <c r="C9" s="6">
+      <c r="B9" s="5">
+        <v>1</v>
+      </c>
+      <c r="C9" s="5">
         <v>1</v>
       </c>
       <c r="D9" s="3">
@@ -1630,10 +1626,10 @@
       <c r="A10" s="2">
         <v>45666</v>
       </c>
-      <c r="B10" s="6">
-        <v>1</v>
-      </c>
-      <c r="C10" s="6">
+      <c r="B10" s="5">
+        <v>1</v>
+      </c>
+      <c r="C10" s="5">
         <v>1</v>
       </c>
       <c r="D10" s="3">
@@ -1647,10 +1643,10 @@
       <c r="A11" s="2">
         <v>45667</v>
       </c>
-      <c r="B11" s="6">
-        <v>1</v>
-      </c>
-      <c r="C11" s="6">
+      <c r="B11" s="5">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5">
         <v>1</v>
       </c>
       <c r="D11" s="3">
@@ -1664,10 +1660,10 @@
       <c r="A12" s="2">
         <v>45668</v>
       </c>
-      <c r="B12" s="6">
-        <v>1</v>
-      </c>
-      <c r="C12" s="6">
+      <c r="B12" s="5">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5">
         <v>1</v>
       </c>
       <c r="D12" s="3">
@@ -1681,10 +1677,10 @@
       <c r="A13" s="2">
         <v>45669</v>
       </c>
-      <c r="B13" s="6">
-        <v>1</v>
-      </c>
-      <c r="C13" s="6">
+      <c r="B13" s="5">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5">
         <v>1</v>
       </c>
       <c r="D13" s="3">
@@ -1698,10 +1694,10 @@
       <c r="A14" s="2">
         <v>45670</v>
       </c>
-      <c r="B14" s="6">
-        <v>1</v>
-      </c>
-      <c r="C14" s="6">
+      <c r="B14" s="5">
+        <v>1</v>
+      </c>
+      <c r="C14" s="5">
         <v>1</v>
       </c>
       <c r="D14" s="3">
@@ -1715,10 +1711,10 @@
       <c r="A15" s="2">
         <v>45671</v>
       </c>
-      <c r="B15" s="6">
-        <v>1</v>
-      </c>
-      <c r="C15" s="6">
+      <c r="B15" s="5">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5">
         <v>1</v>
       </c>
       <c r="D15" s="3">
@@ -1732,10 +1728,10 @@
       <c r="A16" s="2">
         <v>45672</v>
       </c>
-      <c r="B16" s="6">
-        <v>1</v>
-      </c>
-      <c r="C16" s="6">
+      <c r="B16" s="5">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5">
         <v>1</v>
       </c>
       <c r="D16" s="3">
@@ -1749,10 +1745,10 @@
       <c r="A17" s="2">
         <v>45673</v>
       </c>
-      <c r="B17" s="6">
-        <v>1</v>
-      </c>
-      <c r="C17" s="6">
+      <c r="B17" s="5">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5">
         <v>1</v>
       </c>
       <c r="D17" s="3">
@@ -1766,10 +1762,10 @@
       <c r="A18" s="2">
         <v>45674</v>
       </c>
-      <c r="B18" s="6">
-        <v>1</v>
-      </c>
-      <c r="C18" s="6">
+      <c r="B18" s="5">
+        <v>1</v>
+      </c>
+      <c r="C18" s="5">
         <v>1</v>
       </c>
       <c r="D18" s="3">
@@ -1783,10 +1779,10 @@
       <c r="A19" s="2">
         <v>45675</v>
       </c>
-      <c r="B19" s="6">
-        <v>1</v>
-      </c>
-      <c r="C19" s="6">
+      <c r="B19" s="5">
+        <v>1</v>
+      </c>
+      <c r="C19" s="5">
         <v>1</v>
       </c>
       <c r="D19" s="3">
@@ -1800,10 +1796,10 @@
       <c r="A20" s="2">
         <v>45676</v>
       </c>
-      <c r="B20" s="6">
-        <v>1</v>
-      </c>
-      <c r="C20" s="6">
+      <c r="B20" s="5">
+        <v>1</v>
+      </c>
+      <c r="C20" s="5">
         <v>1</v>
       </c>
       <c r="D20" s="3">
@@ -1817,10 +1813,10 @@
       <c r="A21" s="2">
         <v>45677</v>
       </c>
-      <c r="B21" s="6">
-        <v>1</v>
-      </c>
-      <c r="C21" s="6">
+      <c r="B21" s="5">
+        <v>1</v>
+      </c>
+      <c r="C21" s="5">
         <v>1</v>
       </c>
       <c r="D21" s="3">
@@ -1834,10 +1830,10 @@
       <c r="A22" s="2">
         <v>45678</v>
       </c>
-      <c r="B22" s="6">
-        <v>1</v>
-      </c>
-      <c r="C22" s="6">
+      <c r="B22" s="5">
+        <v>1</v>
+      </c>
+      <c r="C22" s="5">
         <v>1</v>
       </c>
       <c r="D22" s="3">
@@ -1851,10 +1847,10 @@
       <c r="A23" s="2">
         <v>45679</v>
       </c>
-      <c r="B23" s="6">
-        <v>1</v>
-      </c>
-      <c r="C23" s="6">
+      <c r="B23" s="5">
+        <v>1</v>
+      </c>
+      <c r="C23" s="5">
         <v>1</v>
       </c>
       <c r="D23" s="3">
@@ -1868,10 +1864,10 @@
       <c r="A24" s="2">
         <v>45680</v>
       </c>
-      <c r="B24" s="6">
-        <v>1</v>
-      </c>
-      <c r="C24" s="6">
+      <c r="B24" s="5">
+        <v>1</v>
+      </c>
+      <c r="C24" s="5">
         <v>1</v>
       </c>
       <c r="D24" s="3">
@@ -1885,10 +1881,10 @@
       <c r="A25" s="2">
         <v>45681</v>
       </c>
-      <c r="B25" s="6">
-        <v>1</v>
-      </c>
-      <c r="C25" s="6">
+      <c r="B25" s="5">
+        <v>1</v>
+      </c>
+      <c r="C25" s="5">
         <v>1</v>
       </c>
       <c r="D25" s="3">
@@ -1902,10 +1898,10 @@
       <c r="A26" s="2">
         <v>45682</v>
       </c>
-      <c r="B26" s="6">
-        <v>1</v>
-      </c>
-      <c r="C26" s="6">
+      <c r="B26" s="5">
+        <v>1</v>
+      </c>
+      <c r="C26" s="5">
         <v>1</v>
       </c>
       <c r="D26" s="3">
@@ -1919,10 +1915,10 @@
       <c r="A27" s="2">
         <v>45683</v>
       </c>
-      <c r="B27" s="6">
-        <v>1</v>
-      </c>
-      <c r="C27" s="6">
+      <c r="B27" s="5">
+        <v>1</v>
+      </c>
+      <c r="C27" s="5">
         <v>1</v>
       </c>
       <c r="D27" s="3">
@@ -1936,10 +1932,10 @@
       <c r="A28" s="2">
         <v>45684</v>
       </c>
-      <c r="B28" s="6">
-        <v>1</v>
-      </c>
-      <c r="C28" s="6">
+      <c r="B28" s="5">
+        <v>1</v>
+      </c>
+      <c r="C28" s="5">
         <v>1</v>
       </c>
       <c r="D28" s="3">
@@ -1953,10 +1949,10 @@
       <c r="A29" s="2">
         <v>45685</v>
       </c>
-      <c r="B29" s="6">
-        <v>1</v>
-      </c>
-      <c r="C29" s="6">
+      <c r="B29" s="5">
+        <v>1</v>
+      </c>
+      <c r="C29" s="5">
         <v>1</v>
       </c>
       <c r="D29" s="3">
@@ -1970,10 +1966,10 @@
       <c r="A30" s="2">
         <v>45686</v>
       </c>
-      <c r="B30" s="6">
-        <v>1</v>
-      </c>
-      <c r="C30" s="6">
+      <c r="B30" s="5">
+        <v>1</v>
+      </c>
+      <c r="C30" s="5">
         <v>1</v>
       </c>
       <c r="D30" s="3">
@@ -1987,10 +1983,10 @@
       <c r="A31" s="2">
         <v>45687</v>
       </c>
-      <c r="B31" s="6">
-        <v>1</v>
-      </c>
-      <c r="C31" s="6">
+      <c r="B31" s="5">
+        <v>1</v>
+      </c>
+      <c r="C31" s="5">
         <v>1</v>
       </c>
       <c r="D31" s="3">
@@ -2004,10 +2000,10 @@
       <c r="A32" s="2">
         <v>45688</v>
       </c>
-      <c r="B32" s="6">
-        <v>1</v>
-      </c>
-      <c r="C32" s="6">
+      <c r="B32" s="5">
+        <v>1</v>
+      </c>
+      <c r="C32" s="5">
         <v>1</v>
       </c>
       <c r="D32" s="3">
@@ -2021,10 +2017,10 @@
       <c r="A33" s="2">
         <v>45689</v>
       </c>
-      <c r="B33" s="6">
-        <v>1</v>
-      </c>
-      <c r="C33" s="6">
+      <c r="B33" s="5">
+        <v>1</v>
+      </c>
+      <c r="C33" s="5">
         <v>1</v>
       </c>
       <c r="D33" s="3">
@@ -2032,6 +2028,284 @@
       </c>
       <c r="E33" s="3">
         <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB18F823-1A3A-443A-9EAF-5FDA541F318B}">
+  <dimension ref="A1:B33"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="10.07421875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.15234375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" s="2">
+        <v>45658</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" s="2">
+        <v>45659</v>
+      </c>
+      <c r="B3">
+        <v>0.95499999999999996</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A4" s="2">
+        <v>45660</v>
+      </c>
+      <c r="B4">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A5" s="2">
+        <v>45661</v>
+      </c>
+      <c r="B5">
+        <v>0.96499999999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" s="2">
+        <v>45662</v>
+      </c>
+      <c r="B6">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" s="2">
+        <v>45663</v>
+      </c>
+      <c r="B7">
+        <v>0.97499999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" s="2">
+        <v>45664</v>
+      </c>
+      <c r="B8">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" s="2">
+        <v>45665</v>
+      </c>
+      <c r="B9">
+        <v>0.98499999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" s="2">
+        <v>45666</v>
+      </c>
+      <c r="B10">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" s="2">
+        <v>45667</v>
+      </c>
+      <c r="B11">
+        <v>0.995</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A12" s="2">
+        <v>45668</v>
+      </c>
+      <c r="B12">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A13" s="2">
+        <v>45669</v>
+      </c>
+      <c r="B13">
+        <v>1.0049999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A14" s="2">
+        <v>45670</v>
+      </c>
+      <c r="B14">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A15" s="2">
+        <v>45671</v>
+      </c>
+      <c r="B15">
+        <v>1.0149999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A16" s="2">
+        <v>45672</v>
+      </c>
+      <c r="B16">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A17" s="2">
+        <v>45673</v>
+      </c>
+      <c r="B17">
+        <v>1.0249999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A18" s="2">
+        <v>45674</v>
+      </c>
+      <c r="B18">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A19" s="2">
+        <v>45675</v>
+      </c>
+      <c r="B19">
+        <v>1.0349999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A20" s="2">
+        <v>45676</v>
+      </c>
+      <c r="B20">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A21" s="2">
+        <v>45677</v>
+      </c>
+      <c r="B21">
+        <v>1.0449999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A22" s="2">
+        <v>45678</v>
+      </c>
+      <c r="B22">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A23" s="2">
+        <v>45679</v>
+      </c>
+      <c r="B23">
+        <v>1.0549999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A24" s="2">
+        <v>45680</v>
+      </c>
+      <c r="B24">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A25" s="2">
+        <v>45681</v>
+      </c>
+      <c r="B25">
+        <v>1.0649999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A26" s="2">
+        <v>45682</v>
+      </c>
+      <c r="B26">
+        <v>1.1200000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A27" s="2">
+        <v>45683</v>
+      </c>
+      <c r="B27">
+        <v>1.075</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A28" s="2">
+        <v>45684</v>
+      </c>
+      <c r="B28">
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A29" s="2">
+        <v>45685</v>
+      </c>
+      <c r="B29">
+        <v>1.085</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A30" s="2">
+        <v>45686</v>
+      </c>
+      <c r="B30">
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A31" s="2">
+        <v>45687</v>
+      </c>
+      <c r="B31">
+        <v>1.095</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A32" s="2">
+        <v>45688</v>
+      </c>
+      <c r="B32">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A33" s="2">
+        <v>45689</v>
+      </c>
+      <c r="B33">
+        <v>1.105</v>
       </c>
     </row>
   </sheetData>

--- a/public/tests/data/test_simple.xlsx
+++ b/public/tests/data/test_simple.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F3DBB8-674F-4138-BAF5-58109BF08BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F03061F5-E618-4294-AAA1-3BF4F7C2E447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="24">
   <si>
     <t>Name</t>
   </si>
@@ -93,22 +93,16 @@
     <t>P2</t>
   </si>
   <si>
-    <t>P1&gt;A1</t>
-  </si>
-  <si>
-    <t>P2&gt;A2</t>
-  </si>
-  <si>
     <t>P3</t>
   </si>
   <si>
-    <t>P3&gt;A1</t>
+    <t>Portfolio Value</t>
   </si>
   <si>
-    <t>P3&gt;A2</t>
+    <t>Asset</t>
   </si>
   <si>
-    <t>Portfolio Value</t>
+    <t>Portfolio</t>
   </si>
 </sst>
 </file>
@@ -529,7 +523,7 @@
         <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
@@ -1005,7 +999,7 @@
         <v>19</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
@@ -1463,7 +1457,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93EA1201-9593-4FA8-BE4A-D6543E3F5A5B}">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.07421875" bestFit="1" customWidth="1"/>
@@ -1471,41 +1465,41 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>23</v>
-      </c>
       <c r="E1" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A2" s="2">
-        <v>45658</v>
-      </c>
-      <c r="B2" s="5">
-        <v>1</v>
-      </c>
-      <c r="C2" s="5">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0.5</v>
+      <c r="A2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
-        <v>45659</v>
+        <v>45658</v>
       </c>
       <c r="B3" s="5">
         <v>1</v>
@@ -1522,7 +1516,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
-        <v>45660</v>
+        <v>45659</v>
       </c>
       <c r="B4" s="5">
         <v>1</v>
@@ -1539,7 +1533,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
-        <v>45661</v>
+        <v>45660</v>
       </c>
       <c r="B5" s="5">
         <v>1</v>
@@ -1556,7 +1550,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
-        <v>45662</v>
+        <v>45661</v>
       </c>
       <c r="B6" s="5">
         <v>1</v>
@@ -1573,7 +1567,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
-        <v>45663</v>
+        <v>45662</v>
       </c>
       <c r="B7" s="5">
         <v>1</v>
@@ -1590,7 +1584,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
-        <v>45664</v>
+        <v>45663</v>
       </c>
       <c r="B8" s="5">
         <v>1</v>
@@ -1607,7 +1601,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
-        <v>45665</v>
+        <v>45664</v>
       </c>
       <c r="B9" s="5">
         <v>1</v>
@@ -1624,7 +1618,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
-        <v>45666</v>
+        <v>45665</v>
       </c>
       <c r="B10" s="5">
         <v>1</v>
@@ -1641,7 +1635,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
-        <v>45667</v>
+        <v>45666</v>
       </c>
       <c r="B11" s="5">
         <v>1</v>
@@ -1658,7 +1652,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
-        <v>45668</v>
+        <v>45667</v>
       </c>
       <c r="B12" s="5">
         <v>1</v>
@@ -1675,7 +1669,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
-        <v>45669</v>
+        <v>45668</v>
       </c>
       <c r="B13" s="5">
         <v>1</v>
@@ -1692,7 +1686,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
-        <v>45670</v>
+        <v>45669</v>
       </c>
       <c r="B14" s="5">
         <v>1</v>
@@ -1709,7 +1703,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
-        <v>45671</v>
+        <v>45670</v>
       </c>
       <c r="B15" s="5">
         <v>1</v>
@@ -1726,7 +1720,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
-        <v>45672</v>
+        <v>45671</v>
       </c>
       <c r="B16" s="5">
         <v>1</v>
@@ -1743,7 +1737,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
-        <v>45673</v>
+        <v>45672</v>
       </c>
       <c r="B17" s="5">
         <v>1</v>
@@ -1760,7 +1754,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
-        <v>45674</v>
+        <v>45673</v>
       </c>
       <c r="B18" s="5">
         <v>1</v>
@@ -1777,7 +1771,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
-        <v>45675</v>
+        <v>45674</v>
       </c>
       <c r="B19" s="5">
         <v>1</v>
@@ -1794,7 +1788,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
-        <v>45676</v>
+        <v>45675</v>
       </c>
       <c r="B20" s="5">
         <v>1</v>
@@ -1811,7 +1805,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
-        <v>45677</v>
+        <v>45676</v>
       </c>
       <c r="B21" s="5">
         <v>1</v>
@@ -1828,7 +1822,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
-        <v>45678</v>
+        <v>45677</v>
       </c>
       <c r="B22" s="5">
         <v>1</v>
@@ -1845,7 +1839,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
-        <v>45679</v>
+        <v>45678</v>
       </c>
       <c r="B23" s="5">
         <v>1</v>
@@ -1862,7 +1856,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
-        <v>45680</v>
+        <v>45679</v>
       </c>
       <c r="B24" s="5">
         <v>1</v>
@@ -1879,7 +1873,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
-        <v>45681</v>
+        <v>45680</v>
       </c>
       <c r="B25" s="5">
         <v>1</v>
@@ -1896,7 +1890,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
-        <v>45682</v>
+        <v>45681</v>
       </c>
       <c r="B26" s="5">
         <v>1</v>
@@ -1913,7 +1907,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
-        <v>45683</v>
+        <v>45682</v>
       </c>
       <c r="B27" s="5">
         <v>1</v>
@@ -1930,7 +1924,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
-        <v>45684</v>
+        <v>45683</v>
       </c>
       <c r="B28" s="5">
         <v>1</v>
@@ -1947,7 +1941,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
-        <v>45685</v>
+        <v>45684</v>
       </c>
       <c r="B29" s="5">
         <v>1</v>
@@ -1964,7 +1958,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
-        <v>45686</v>
+        <v>45685</v>
       </c>
       <c r="B30" s="5">
         <v>1</v>
@@ -1981,7 +1975,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
-        <v>45687</v>
+        <v>45686</v>
       </c>
       <c r="B31" s="5">
         <v>1</v>
@@ -1998,7 +1992,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
-        <v>45688</v>
+        <v>45687</v>
       </c>
       <c r="B32" s="5">
         <v>1</v>
@@ -2015,18 +2009,35 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
+        <v>45688</v>
+      </c>
+      <c r="B33" s="5">
+        <v>1</v>
+      </c>
+      <c r="C33" s="5">
+        <v>1</v>
+      </c>
+      <c r="D33" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A34" s="2">
         <v>45689</v>
       </c>
-      <c r="B33" s="5">
-        <v>1</v>
-      </c>
-      <c r="C33" s="5">
-        <v>1</v>
-      </c>
-      <c r="D33" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="E33" s="3">
+      <c r="B34" s="5">
+        <v>1</v>
+      </c>
+      <c r="C34" s="5">
+        <v>1</v>
+      </c>
+      <c r="D34" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E34" s="3">
         <v>0.5</v>
       </c>
     </row>
@@ -2049,7 +2060,7 @@
         <v>17</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">

--- a/public/tests/data/test_simple.xlsx
+++ b/public/tests/data/test_simple.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F03061F5-E618-4294-AAA1-3BF4F7C2E447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCFA0F90-FB7D-483F-A30E-D50A26EC4C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,10 +21,21 @@
     <sheet name="Expected_Portfolio_Weights" sheetId="7" r:id="rId6"/>
     <sheet name="Sheet5" sheetId="9" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1542,10 +1553,12 @@
         <v>1</v>
       </c>
       <c r="D5" s="3">
-        <v>0.5</v>
+        <f>(D4 * (Prices!$B3/Prices!$B2)) / ((D4 * (Prices!$B3/Prices!$B2)) + (E4 * (Prices!$C3/Prices!$C2)))</f>
+        <v>0.52879581151832455</v>
       </c>
       <c r="E5" s="3">
-        <v>0.5</v>
+        <f>(E4 * (Prices!$C3/Prices!$C2)) / ((D4 * (Prices!$B3/Prices!$B2)) + (E4 * (Prices!$C3/Prices!$C2)))</f>
+        <v>0.47120418848167539</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
@@ -1559,10 +1572,12 @@
         <v>1</v>
       </c>
       <c r="D6" s="3">
-        <v>0.5</v>
+        <f>(D5 * (Prices!$B4/Prices!$B3)) / ((D5 * (Prices!$B4/Prices!$B3)) + (E5 * (Prices!$C4/Prices!$C3)))</f>
+        <v>0.50495049504950495</v>
       </c>
       <c r="E6" s="3">
-        <v>0.5</v>
+        <f>(E5 * (Prices!$C4/Prices!$C3)) / ((D5 * (Prices!$B4/Prices!$B3)) + (E5 * (Prices!$C4/Prices!$C3)))</f>
+        <v>0.4950495049504951</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
@@ -1576,10 +1591,12 @@
         <v>1</v>
       </c>
       <c r="D7" s="3">
-        <v>0.5</v>
+        <f>(D6 * (Prices!$B5/Prices!$B4)) / ((D6 * (Prices!$B5/Prices!$B4)) + (E6 * (Prices!$C5/Prices!$C4)))</f>
+        <v>0.53367875647668395</v>
       </c>
       <c r="E7" s="3">
-        <v>0.5</v>
+        <f>(E6 * (Prices!$C5/Prices!$C4)) / ((D6 * (Prices!$B5/Prices!$B4)) + (E6 * (Prices!$C5/Prices!$C4)))</f>
+        <v>0.46632124352331611</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
@@ -1593,10 +1610,12 @@
         <v>1</v>
       </c>
       <c r="D8" s="3">
-        <v>0.5</v>
+        <f>(D7 * (Prices!$B6/Prices!$B5)) / ((D7 * (Prices!$B6/Prices!$B5)) + (E7 * (Prices!$C6/Prices!$C5)))</f>
+        <v>0.50980392156862742</v>
       </c>
       <c r="E8" s="3">
-        <v>0.5</v>
+        <f>(E7 * (Prices!$C6/Prices!$C5)) / ((D7 * (Prices!$B6/Prices!$B5)) + (E7 * (Prices!$C6/Prices!$C5)))</f>
+        <v>0.49019607843137253</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
@@ -1610,10 +1629,12 @@
         <v>1</v>
       </c>
       <c r="D9" s="3">
-        <v>0.5</v>
+        <f>(D8 * (Prices!$B7/Prices!$B6)) / ((D8 * (Prices!$B7/Prices!$B6)) + (E8 * (Prices!$C7/Prices!$C6)))</f>
+        <v>0.53846153846153844</v>
       </c>
       <c r="E9" s="3">
-        <v>0.5</v>
+        <f>(E8 * (Prices!$C7/Prices!$C6)) / ((D8 * (Prices!$B7/Prices!$B6)) + (E8 * (Prices!$C7/Prices!$C6)))</f>
+        <v>0.46153846153846156</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
@@ -1627,10 +1648,12 @@
         <v>1</v>
       </c>
       <c r="D10" s="3">
-        <v>0.5</v>
+        <f>(D9 * (Prices!$B8/Prices!$B7)) / ((D9 * (Prices!$B8/Prices!$B7)) + (E9 * (Prices!$C8/Prices!$C7)))</f>
+        <v>0.5145631067961165</v>
       </c>
       <c r="E10" s="3">
-        <v>0.5</v>
+        <f>(E9 * (Prices!$C8/Prices!$C7)) / ((D9 * (Prices!$B8/Prices!$B7)) + (E9 * (Prices!$C8/Prices!$C7)))</f>
+        <v>0.48543689320388356</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
@@ -1644,10 +1667,12 @@
         <v>1</v>
       </c>
       <c r="D11" s="3">
-        <v>0.5</v>
+        <f>(D10 * (Prices!$B9/Prices!$B8)) / ((D10 * (Prices!$B9/Prices!$B8)) + (E10 * (Prices!$C9/Prices!$C8)))</f>
+        <v>0.54314720812182737</v>
       </c>
       <c r="E11" s="3">
-        <v>0.5</v>
+        <f>(E10 * (Prices!$C9/Prices!$C8)) / ((D10 * (Prices!$B9/Prices!$B8)) + (E10 * (Prices!$C9/Prices!$C8)))</f>
+        <v>0.45685279187817257</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
@@ -1661,10 +1686,12 @@
         <v>1</v>
       </c>
       <c r="D12" s="3">
-        <v>0.5</v>
+        <f>(D11 * (Prices!$B10/Prices!$B9)) / ((D11 * (Prices!$B10/Prices!$B9)) + (E11 * (Prices!$C10/Prices!$C9)))</f>
+        <v>0.51923076923076916</v>
       </c>
       <c r="E12" s="3">
-        <v>0.5</v>
+        <f>(E11 * (Prices!$C10/Prices!$C9)) / ((D11 * (Prices!$B10/Prices!$B9)) + (E11 * (Prices!$C10/Prices!$C9)))</f>
+        <v>0.48076923076923084</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.4">
@@ -1678,10 +1705,12 @@
         <v>1</v>
       </c>
       <c r="D13" s="3">
-        <v>0.5</v>
+        <f>(D12 * (Prices!$B11/Prices!$B10)) / ((D12 * (Prices!$B11/Prices!$B10)) + (E12 * (Prices!$C11/Prices!$C10)))</f>
+        <v>0.54773869346733661</v>
       </c>
       <c r="E13" s="3">
-        <v>0.5</v>
+        <f>(E12 * (Prices!$C11/Prices!$C10)) / ((D12 * (Prices!$B11/Prices!$B10)) + (E12 * (Prices!$C11/Prices!$C10)))</f>
+        <v>0.45226130653266344</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
@@ -1695,10 +1724,12 @@
         <v>1</v>
       </c>
       <c r="D14" s="3">
-        <v>0.5</v>
+        <f>(D13 * (Prices!$B12/Prices!$B11)) / ((D13 * (Prices!$B12/Prices!$B11)) + (E13 * (Prices!$C12/Prices!$C11)))</f>
+        <v>0.52380952380952372</v>
       </c>
       <c r="E14" s="3">
-        <v>0.5</v>
+        <f>(E13 * (Prices!$C12/Prices!$C11)) / ((D13 * (Prices!$B12/Prices!$B11)) + (E13 * (Prices!$C12/Prices!$C11)))</f>
+        <v>0.47619047619047628</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
@@ -1712,10 +1743,12 @@
         <v>1</v>
       </c>
       <c r="D15" s="3">
-        <v>0.5</v>
+        <f>(D14 * (Prices!$B13/Prices!$B12)) / ((D14 * (Prices!$B13/Prices!$B12)) + (E14 * (Prices!$C13/Prices!$C12)))</f>
+        <v>0.55223880597014918</v>
       </c>
       <c r="E15" s="3">
-        <v>0.5</v>
+        <f>(E14 * (Prices!$C13/Prices!$C12)) / ((D14 * (Prices!$B13/Prices!$B12)) + (E14 * (Prices!$C13/Prices!$C12)))</f>
+        <v>0.44776119402985087</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
@@ -1729,10 +1762,12 @@
         <v>1</v>
       </c>
       <c r="D16" s="3">
-        <v>0.5</v>
+        <f>(D15 * (Prices!$B14/Prices!$B13)) / ((D15 * (Prices!$B14/Prices!$B13)) + (E15 * (Prices!$C14/Prices!$C13)))</f>
+        <v>0.52830188679245271</v>
       </c>
       <c r="E16" s="3">
-        <v>0.5</v>
+        <f>(E15 * (Prices!$C14/Prices!$C13)) / ((D15 * (Prices!$B14/Prices!$B13)) + (E15 * (Prices!$C14/Prices!$C13)))</f>
+        <v>0.47169811320754729</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.4">
@@ -1746,10 +1781,12 @@
         <v>1</v>
       </c>
       <c r="D17" s="3">
-        <v>0.5</v>
+        <f>(D16 * (Prices!$B15/Prices!$B14)) / ((D16 * (Prices!$B15/Prices!$B14)) + (E16 * (Prices!$C15/Prices!$C14)))</f>
+        <v>0.55665024630541859</v>
       </c>
       <c r="E17" s="3">
-        <v>0.5</v>
+        <f>(E16 * (Prices!$C15/Prices!$C14)) / ((D16 * (Prices!$B15/Prices!$B14)) + (E16 * (Prices!$C15/Prices!$C14)))</f>
+        <v>0.44334975369458146</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.4">
@@ -1763,10 +1800,12 @@
         <v>1</v>
       </c>
       <c r="D18" s="3">
-        <v>0.5</v>
+        <f>(D17 * (Prices!$B16/Prices!$B15)) / ((D17 * (Prices!$B16/Prices!$B15)) + (E17 * (Prices!$C16/Prices!$C15)))</f>
+        <v>0.53271028037383161</v>
       </c>
       <c r="E18" s="3">
-        <v>0.5</v>
+        <f>(E17 * (Prices!$C16/Prices!$C15)) / ((D17 * (Prices!$B16/Prices!$B15)) + (E17 * (Prices!$C16/Prices!$C15)))</f>
+        <v>0.46728971962616844</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.4">
@@ -1780,10 +1819,12 @@
         <v>1</v>
       </c>
       <c r="D19" s="3">
-        <v>0.5</v>
+        <f>(D18 * (Prices!$B17/Prices!$B16)) / ((D18 * (Prices!$B17/Prices!$B16)) + (E18 * (Prices!$C17/Prices!$C16)))</f>
+        <v>0.56097560975609739</v>
       </c>
       <c r="E19" s="3">
-        <v>0.5</v>
+        <f>(E18 * (Prices!$C17/Prices!$C16)) / ((D18 * (Prices!$B17/Prices!$B16)) + (E18 * (Prices!$C17/Prices!$C16)))</f>
+        <v>0.43902439024390261</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.4">
@@ -1797,10 +1838,12 @@
         <v>1</v>
       </c>
       <c r="D20" s="3">
-        <v>0.5</v>
+        <f>(D19 * (Prices!$B18/Prices!$B17)) / ((D19 * (Prices!$B18/Prices!$B17)) + (E19 * (Prices!$C18/Prices!$C17)))</f>
+        <v>0.53703703703703687</v>
       </c>
       <c r="E20" s="3">
-        <v>0.5</v>
+        <f>(E19 * (Prices!$C18/Prices!$C17)) / ((D19 * (Prices!$B18/Prices!$B17)) + (E19 * (Prices!$C18/Prices!$C17)))</f>
+        <v>0.46296296296296313</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.4">
@@ -1814,10 +1857,12 @@
         <v>1</v>
       </c>
       <c r="D21" s="3">
-        <v>0.5</v>
+        <f>(D20 * (Prices!$B19/Prices!$B18)) / ((D20 * (Prices!$B19/Prices!$B18)) + (E20 * (Prices!$C19/Prices!$C18)))</f>
+        <v>0.56521739130434767</v>
       </c>
       <c r="E21" s="3">
-        <v>0.5</v>
+        <f>(E20 * (Prices!$C19/Prices!$C18)) / ((D20 * (Prices!$B19/Prices!$B18)) + (E20 * (Prices!$C19/Prices!$C18)))</f>
+        <v>0.43478260869565233</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.4">
@@ -1831,10 +1876,12 @@
         <v>1</v>
       </c>
       <c r="D22" s="3">
-        <v>0.5</v>
+        <f>(D21 * (Prices!$B20/Prices!$B19)) / ((D21 * (Prices!$B20/Prices!$B19)) + (E21 * (Prices!$C20/Prices!$C19)))</f>
+        <v>0.54128440366972463</v>
       </c>
       <c r="E22" s="3">
-        <v>0.5</v>
+        <f>(E21 * (Prices!$C20/Prices!$C19)) / ((D21 * (Prices!$B20/Prices!$B19)) + (E21 * (Prices!$C20/Prices!$C19)))</f>
+        <v>0.45871559633027542</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.4">
@@ -1848,10 +1895,12 @@
         <v>1</v>
       </c>
       <c r="D23" s="3">
-        <v>0.5</v>
+        <f>(D22 * (Prices!$B21/Prices!$B20)) / ((D22 * (Prices!$B21/Prices!$B20)) + (E22 * (Prices!$C21/Prices!$C20)))</f>
+        <v>0.56937799043062187</v>
       </c>
       <c r="E23" s="3">
-        <v>0.5</v>
+        <f>(E22 * (Prices!$C21/Prices!$C20)) / ((D22 * (Prices!$B21/Prices!$B20)) + (E22 * (Prices!$C21/Prices!$C20)))</f>
+        <v>0.43062200956937818</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.4">
@@ -1865,10 +1914,12 @@
         <v>1</v>
       </c>
       <c r="D24" s="3">
-        <v>0.5</v>
+        <f>(D23 * (Prices!$B22/Prices!$B21)) / ((D23 * (Prices!$B22/Prices!$B21)) + (E23 * (Prices!$C22/Prices!$C21)))</f>
+        <v>0.5454545454545453</v>
       </c>
       <c r="E24" s="3">
-        <v>0.5</v>
+        <f>(E23 * (Prices!$C22/Prices!$C21)) / ((D23 * (Prices!$B22/Prices!$B21)) + (E23 * (Prices!$C22/Prices!$C21)))</f>
+        <v>0.4545454545454547</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.4">
@@ -1882,10 +1933,12 @@
         <v>1</v>
       </c>
       <c r="D25" s="3">
-        <v>0.5</v>
+        <f>(D24 * (Prices!$B23/Prices!$B22)) / ((D24 * (Prices!$B23/Prices!$B22)) + (E24 * (Prices!$C23/Prices!$C22)))</f>
+        <v>0.57345971563981035</v>
       </c>
       <c r="E25" s="3">
-        <v>0.5</v>
+        <f>(E24 * (Prices!$C23/Prices!$C22)) / ((D24 * (Prices!$B23/Prices!$B22)) + (E24 * (Prices!$C23/Prices!$C22)))</f>
+        <v>0.42654028436018976</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.4">
@@ -1899,10 +1952,12 @@
         <v>1</v>
       </c>
       <c r="D26" s="3">
-        <v>0.5</v>
+        <f>(D25 * (Prices!$B24/Prices!$B23)) / ((D25 * (Prices!$B24/Prices!$B23)) + (E25 * (Prices!$C24/Prices!$C23)))</f>
+        <v>0.54954954954954938</v>
       </c>
       <c r="E26" s="3">
-        <v>0.5</v>
+        <f>(E25 * (Prices!$C24/Prices!$C23)) / ((D25 * (Prices!$B24/Prices!$B23)) + (E25 * (Prices!$C24/Prices!$C23)))</f>
+        <v>0.45045045045045068</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.4">
@@ -1916,10 +1971,12 @@
         <v>1</v>
       </c>
       <c r="D27" s="3">
-        <v>0.5</v>
+        <f>(D26 * (Prices!$B25/Prices!$B24)) / ((D26 * (Prices!$B25/Prices!$B24)) + (E26 * (Prices!$C25/Prices!$C24)))</f>
+        <v>0.57746478873239415</v>
       </c>
       <c r="E27" s="3">
-        <v>0.5</v>
+        <f>(E26 * (Prices!$C25/Prices!$C24)) / ((D26 * (Prices!$B25/Prices!$B24)) + (E26 * (Prices!$C25/Prices!$C24)))</f>
+        <v>0.42253521126760585</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.4">
@@ -1933,10 +1990,12 @@
         <v>1</v>
       </c>
       <c r="D28" s="3">
-        <v>0.5</v>
+        <f>(D27 * (Prices!$B26/Prices!$B25)) / ((D27 * (Prices!$B26/Prices!$B25)) + (E27 * (Prices!$C26/Prices!$C25)))</f>
+        <v>0.55357142857142827</v>
       </c>
       <c r="E28" s="3">
-        <v>0.5</v>
+        <f>(E27 * (Prices!$C26/Prices!$C25)) / ((D27 * (Prices!$B26/Prices!$B25)) + (E27 * (Prices!$C26/Prices!$C25)))</f>
+        <v>0.44642857142857167</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.4">
@@ -1950,10 +2009,12 @@
         <v>1</v>
       </c>
       <c r="D29" s="3">
-        <v>0.5</v>
+        <f>(D28 * (Prices!$B27/Prices!$B26)) / ((D28 * (Prices!$B27/Prices!$B26)) + (E28 * (Prices!$C27/Prices!$C26)))</f>
+        <v>0.581395348837209</v>
       </c>
       <c r="E29" s="3">
-        <v>0.5</v>
+        <f>(E28 * (Prices!$C27/Prices!$C26)) / ((D28 * (Prices!$B27/Prices!$B26)) + (E28 * (Prices!$C27/Prices!$C26)))</f>
+        <v>0.418604651162791</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.4">
@@ -1967,10 +2028,12 @@
         <v>1</v>
       </c>
       <c r="D30" s="3">
-        <v>0.5</v>
+        <f>(D29 * (Prices!$B28/Prices!$B27)) / ((D29 * (Prices!$B28/Prices!$B27)) + (E29 * (Prices!$C28/Prices!$C27)))</f>
+        <v>0.55752212389380507</v>
       </c>
       <c r="E30" s="3">
-        <v>0.5</v>
+        <f>(E29 * (Prices!$C28/Prices!$C27)) / ((D29 * (Prices!$B28/Prices!$B27)) + (E29 * (Prices!$C28/Prices!$C27)))</f>
+        <v>0.44247787610619504</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.4">
@@ -1984,10 +2047,12 @@
         <v>1</v>
       </c>
       <c r="D31" s="3">
-        <v>0.5</v>
+        <f>(D30 * (Prices!$B29/Prices!$B28)) / ((D30 * (Prices!$B29/Prices!$B28)) + (E30 * (Prices!$C29/Prices!$C28)))</f>
+        <v>0.58525345622119784</v>
       </c>
       <c r="E31" s="3">
-        <v>0.5</v>
+        <f>(E30 * (Prices!$C29/Prices!$C28)) / ((D30 * (Prices!$B29/Prices!$B28)) + (E30 * (Prices!$C29/Prices!$C28)))</f>
+        <v>0.41474654377880216</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.4">
@@ -2001,10 +2066,12 @@
         <v>1</v>
       </c>
       <c r="D32" s="3">
-        <v>0.5</v>
+        <f>(D31 * (Prices!$B30/Prices!$B29)) / ((D31 * (Prices!$B30/Prices!$B29)) + (E31 * (Prices!$C30/Prices!$C29)))</f>
+        <v>0.56140350877192946</v>
       </c>
       <c r="E32" s="3">
-        <v>0.5</v>
+        <f>(E31 * (Prices!$C30/Prices!$C29)) / ((D31 * (Prices!$B30/Prices!$B29)) + (E31 * (Prices!$C30/Prices!$C29)))</f>
+        <v>0.43859649122807048</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.4">
@@ -2018,10 +2085,12 @@
         <v>1</v>
       </c>
       <c r="D33" s="3">
-        <v>0.5</v>
+        <f>(D32 * (Prices!$B31/Prices!$B30)) / ((D32 * (Prices!$B31/Prices!$B30)) + (E32 * (Prices!$C31/Prices!$C30)))</f>
+        <v>0.58904109589041065</v>
       </c>
       <c r="E33" s="3">
-        <v>0.5</v>
+        <f>(E32 * (Prices!$C31/Prices!$C30)) / ((D32 * (Prices!$B31/Prices!$B30)) + (E32 * (Prices!$C31/Prices!$C30)))</f>
+        <v>0.41095890410958935</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.4">
@@ -2035,10 +2104,12 @@
         <v>1</v>
       </c>
       <c r="D34" s="3">
-        <v>0.5</v>
+        <f>(D33 * (Prices!$B32/Prices!$B31)) / ((D33 * (Prices!$B32/Prices!$B31)) + (E33 * (Prices!$C32/Prices!$C31)))</f>
+        <v>0.56521739130434756</v>
       </c>
       <c r="E34" s="3">
-        <v>0.5</v>
+        <f>(E33 * (Prices!$C32/Prices!$C31)) / ((D33 * (Prices!$B32/Prices!$B31)) + (E33 * (Prices!$C32/Prices!$C31)))</f>
+        <v>0.43478260869565249</v>
       </c>
     </row>
   </sheetData>

--- a/public/tests/data/test_simple.xlsx
+++ b/public/tests/data/test_simple.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCFA0F90-FB7D-483F-A30E-D50A26EC4C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37E6FABC-C8ED-4DD3-B8AE-C8D7B7A9D4C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="Portfolios" sheetId="2" r:id="rId2"/>
     <sheet name="Assets" sheetId="4" r:id="rId3"/>
     <sheet name="Prices" sheetId="5" r:id="rId4"/>
-    <sheet name="Expected_Portfolio_Values" sheetId="6" r:id="rId5"/>
-    <sheet name="Expected_Portfolio_Weights" sheetId="7" r:id="rId6"/>
-    <sheet name="Sheet5" sheetId="9" r:id="rId7"/>
+    <sheet name="Expected_Values" sheetId="6" r:id="rId5"/>
+    <sheet name="Expected_Weights" sheetId="7" r:id="rId6"/>
+    <sheet name="Expected_Stats" sheetId="10" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="23">
   <si>
     <t>Name</t>
   </si>
@@ -105,9 +105,6 @@
   </si>
   <si>
     <t>P3</t>
-  </si>
-  <si>
-    <t>Portfolio Value</t>
   </si>
   <si>
     <t>Asset</t>
@@ -1476,7 +1473,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>18</v>
@@ -1493,7 +1490,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>10</v>
@@ -2118,279 +2115,10 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB18F823-1A3A-443A-9EAF-5FDA541F318B}">
-  <dimension ref="A1:B33"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C9C66B4-691D-4E6C-9B58-26BA46864B57}">
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="10.07421875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.15234375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" s="2">
-        <v>45658</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" s="2">
-        <v>45659</v>
-      </c>
-      <c r="B3">
-        <v>0.95499999999999996</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A4" s="2">
-        <v>45660</v>
-      </c>
-      <c r="B4">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A5" s="2">
-        <v>45661</v>
-      </c>
-      <c r="B5">
-        <v>0.96499999999999997</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" s="2">
-        <v>45662</v>
-      </c>
-      <c r="B6">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" s="2">
-        <v>45663</v>
-      </c>
-      <c r="B7">
-        <v>0.97499999999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A8" s="2">
-        <v>45664</v>
-      </c>
-      <c r="B8">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" s="2">
-        <v>45665</v>
-      </c>
-      <c r="B9">
-        <v>0.98499999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A10" s="2">
-        <v>45666</v>
-      </c>
-      <c r="B10">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A11" s="2">
-        <v>45667</v>
-      </c>
-      <c r="B11">
-        <v>0.995</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A12" s="2">
-        <v>45668</v>
-      </c>
-      <c r="B12">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A13" s="2">
-        <v>45669</v>
-      </c>
-      <c r="B13">
-        <v>1.0049999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A14" s="2">
-        <v>45670</v>
-      </c>
-      <c r="B14">
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A15" s="2">
-        <v>45671</v>
-      </c>
-      <c r="B15">
-        <v>1.0149999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A16" s="2">
-        <v>45672</v>
-      </c>
-      <c r="B16">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A17" s="2">
-        <v>45673</v>
-      </c>
-      <c r="B17">
-        <v>1.0249999999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A18" s="2">
-        <v>45674</v>
-      </c>
-      <c r="B18">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A19" s="2">
-        <v>45675</v>
-      </c>
-      <c r="B19">
-        <v>1.0349999999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A20" s="2">
-        <v>45676</v>
-      </c>
-      <c r="B20">
-        <v>1.0900000000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A21" s="2">
-        <v>45677</v>
-      </c>
-      <c r="B21">
-        <v>1.0449999999999999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A22" s="2">
-        <v>45678</v>
-      </c>
-      <c r="B22">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A23" s="2">
-        <v>45679</v>
-      </c>
-      <c r="B23">
-        <v>1.0549999999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A24" s="2">
-        <v>45680</v>
-      </c>
-      <c r="B24">
-        <v>1.1100000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A25" s="2">
-        <v>45681</v>
-      </c>
-      <c r="B25">
-        <v>1.0649999999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A26" s="2">
-        <v>45682</v>
-      </c>
-      <c r="B26">
-        <v>1.1200000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A27" s="2">
-        <v>45683</v>
-      </c>
-      <c r="B27">
-        <v>1.075</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A28" s="2">
-        <v>45684</v>
-      </c>
-      <c r="B28">
-        <v>1.1299999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A29" s="2">
-        <v>45685</v>
-      </c>
-      <c r="B29">
-        <v>1.085</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A30" s="2">
-        <v>45686</v>
-      </c>
-      <c r="B30">
-        <v>1.1399999999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A31" s="2">
-        <v>45687</v>
-      </c>
-      <c r="B31">
-        <v>1.095</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A32" s="2">
-        <v>45688</v>
-      </c>
-      <c r="B32">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A33" s="2">
-        <v>45689</v>
-      </c>
-      <c r="B33">
-        <v>1.105</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/public/tests/data/test_simple.xlsx
+++ b/public/tests/data/test_simple.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37E6FABC-C8ED-4DD3-B8AE-C8D7B7A9D4C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C34F83-B53B-4301-B3B9-BFC22F7A2E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="62">
   <si>
     <t>Name</t>
   </si>
@@ -111,6 +111,123 @@
   </si>
   <si>
     <t>Portfolio</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>End</t>
+  </si>
+  <si>
+    <t>RB Check</t>
+  </si>
+  <si>
+    <t>RB Type</t>
+  </si>
+  <si>
+    <t>Total Return %</t>
+  </si>
+  <si>
+    <t>CAGR %</t>
+  </si>
+  <si>
+    <t>Volatility %</t>
+  </si>
+  <si>
+    <t>Sharpe</t>
+  </si>
+  <si>
+    <t>Sortino</t>
+  </si>
+  <si>
+    <t>Max Drawdown %</t>
+  </si>
+  <si>
+    <t>Avg Drawdown %</t>
+  </si>
+  <si>
+    <t>Max Drawdown Period</t>
+  </si>
+  <si>
+    <t>daily</t>
+  </si>
+  <si>
+    <t>sigma</t>
+  </si>
+  <si>
+    <t>150.55</t>
+  </si>
+  <si>
+    <t>6.62</t>
+  </si>
+  <si>
+    <t>5.97</t>
+  </si>
+  <si>
+    <t>1.07</t>
+  </si>
+  <si>
+    <t>1.58</t>
+  </si>
+  <si>
+    <t>-13.56</t>
+  </si>
+  <si>
+    <t>-1.11</t>
+  </si>
+  <si>
+    <t>1.15 years</t>
+  </si>
+  <si>
+    <t>160.25</t>
+  </si>
+  <si>
+    <t>6.90</t>
+  </si>
+  <si>
+    <t>6.22</t>
+  </si>
+  <si>
+    <t>1.56</t>
+  </si>
+  <si>
+    <t>-13.93</t>
+  </si>
+  <si>
+    <t>-1.12</t>
+  </si>
+  <si>
+    <t>1.34 years</t>
+  </si>
+  <si>
+    <t>half-year</t>
+  </si>
+  <si>
+    <t>full</t>
+  </si>
+  <si>
+    <t>206.28</t>
+  </si>
+  <si>
+    <t>8.12</t>
+  </si>
+  <si>
+    <t>7.83</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>1.45</t>
+  </si>
+  <si>
+    <t>-13.54</t>
+  </si>
+  <si>
+    <t>-1.26</t>
+  </si>
+  <si>
+    <t>1.08 years</t>
   </si>
 </sst>
 </file>
@@ -2116,9 +2233,187 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C9C66B4-691D-4E6C-9B58-26BA46864B57}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="8.07421875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.07421875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.53515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.61328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.23046875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.53515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.15234375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.61328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.84375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.07421875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.4609375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.07421875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="2">
+        <v>40877</v>
+      </c>
+      <c r="C2" s="2">
+        <v>46112</v>
+      </c>
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2">
+        <v>40877</v>
+      </c>
+      <c r="C3" s="2">
+        <v>46112</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K3" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" t="s">
+        <v>50</v>
+      </c>
+      <c r="M3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="2">
+        <v>40877</v>
+      </c>
+      <c r="C4" s="2">
+        <v>46112</v>
+      </c>
+      <c r="D4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" t="s">
+        <v>57</v>
+      </c>
+      <c r="J4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L4" t="s">
+        <v>60</v>
+      </c>
+      <c r="M4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/public/tests/data/test_simple.xlsx
+++ b/public/tests/data/test_simple.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C34F83-B53B-4301-B3B9-BFC22F7A2E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71227824-674B-4214-980A-60497E825BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,6 +20,7 @@
     <sheet name="Expected_Values" sheetId="6" r:id="rId5"/>
     <sheet name="Expected_Weights" sheetId="7" r:id="rId6"/>
     <sheet name="Expected_Stats" sheetId="10" r:id="rId7"/>
+    <sheet name="Sheet7" sheetId="11" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="47">
   <si>
     <t>Name</t>
   </si>
@@ -149,85 +150,40 @@
     <t>Max Drawdown Period</t>
   </si>
   <si>
-    <t>daily</t>
-  </si>
-  <si>
-    <t>sigma</t>
-  </si>
-  <si>
-    <t>150.55</t>
-  </si>
-  <si>
-    <t>6.62</t>
-  </si>
-  <si>
-    <t>5.97</t>
-  </si>
-  <si>
-    <t>1.07</t>
-  </si>
-  <si>
-    <t>1.58</t>
-  </si>
-  <si>
-    <t>-13.56</t>
-  </si>
-  <si>
-    <t>-1.11</t>
-  </si>
-  <si>
     <t>1.15 years</t>
   </si>
   <si>
-    <t>160.25</t>
-  </si>
-  <si>
-    <t>6.90</t>
-  </si>
-  <si>
-    <t>6.22</t>
-  </si>
-  <si>
-    <t>1.56</t>
-  </si>
-  <si>
-    <t>-13.93</t>
-  </si>
-  <si>
-    <t>-1.12</t>
-  </si>
-  <si>
     <t>1.34 years</t>
   </si>
   <si>
-    <t>half-year</t>
-  </si>
-  <si>
     <t>full</t>
   </si>
   <si>
-    <t>206.28</t>
-  </si>
-  <si>
-    <t>8.12</t>
-  </si>
-  <si>
-    <t>7.83</t>
-  </si>
-  <si>
-    <t>1.00</t>
-  </si>
-  <si>
-    <t>1.45</t>
-  </si>
-  <si>
-    <t>-13.54</t>
-  </si>
-  <si>
-    <t>-1.26</t>
-  </si>
-  <si>
     <t>1.08 years</t>
+  </si>
+  <si>
+    <t>once</t>
+  </si>
+  <si>
+    <t>$$CAGR = (1.31)^{\frac{365.25}{31}} - 1 \approx 23.0836 \rightarrow 2308.36\%$$</t>
+  </si>
+  <si>
+    <t>Portfolio 1 ($100\%$ A1):</t>
+  </si>
+  <si>
+    <t>Portfolio 2 ($100\%$ A2):</t>
+  </si>
+  <si>
+    <t>$$CAGR = (0.90)^{\frac{365.25}{31}} - 1 \approx -0.7112 \rightarrow -71.1\%$$</t>
+  </si>
+  <si>
+    <t>Portfolio 3 ($50/50$ Drift):</t>
+  </si>
+  <si>
+    <t>$$CAGR = (1.105)^{\frac{365.25}{31}} - 1 \approx 2.2427 \rightarrow 224.27\%$$</t>
+  </si>
+  <si>
+    <t>inf</t>
   </si>
 </sst>
 </file>
@@ -282,12 +238,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1110,20 +1067,20 @@
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.07421875" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="9.23046875" style="7"/>
+    <col min="2" max="4" width="9.23046875" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1131,13 +1088,13 @@
       <c r="A2" s="2">
         <v>45658</v>
       </c>
-      <c r="B2" s="7">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7">
-        <v>1</v>
-      </c>
-      <c r="D2" s="7">
+      <c r="B2" s="8">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8">
+        <v>1</v>
+      </c>
+      <c r="D2" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1145,13 +1102,13 @@
       <c r="A3" s="2">
         <v>45659</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="8">
         <v>1.01</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="8">
         <v>0.9</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="8">
         <v>0.95499999999999996</v>
       </c>
     </row>
@@ -1159,13 +1116,13 @@
       <c r="A4" s="2">
         <v>45660</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="8">
         <v>1.02</v>
       </c>
-      <c r="C4" s="7">
-        <v>1</v>
-      </c>
-      <c r="D4" s="7">
+      <c r="C4" s="8">
+        <v>1</v>
+      </c>
+      <c r="D4" s="8">
         <v>1.01</v>
       </c>
     </row>
@@ -1173,13 +1130,13 @@
       <c r="A5" s="2">
         <v>45661</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="8">
         <v>1.03</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="8">
         <v>0.9</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="8">
         <v>0.96499999999999997</v>
       </c>
     </row>
@@ -1187,13 +1144,13 @@
       <c r="A6" s="2">
         <v>45662</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="8">
         <v>1.04</v>
       </c>
-      <c r="C6" s="7">
-        <v>1</v>
-      </c>
-      <c r="D6" s="7">
+      <c r="C6" s="8">
+        <v>1</v>
+      </c>
+      <c r="D6" s="8">
         <v>1.02</v>
       </c>
     </row>
@@ -1201,13 +1158,13 @@
       <c r="A7" s="2">
         <v>45663</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="8">
         <v>1.05</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="8">
         <v>0.9</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="8">
         <v>0.97499999999999998</v>
       </c>
     </row>
@@ -1215,13 +1172,13 @@
       <c r="A8" s="2">
         <v>45664</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="8">
         <v>1.06</v>
       </c>
-      <c r="C8" s="7">
-        <v>1</v>
-      </c>
-      <c r="D8" s="7">
+      <c r="C8" s="8">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8">
         <v>1.03</v>
       </c>
     </row>
@@ -1229,13 +1186,13 @@
       <c r="A9" s="2">
         <v>45665</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="8">
         <v>1.07</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="8">
         <v>0.9</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="8">
         <v>0.98499999999999999</v>
       </c>
     </row>
@@ -1243,13 +1200,13 @@
       <c r="A10" s="2">
         <v>45666</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="8">
         <v>1.08</v>
       </c>
-      <c r="C10" s="7">
-        <v>1</v>
-      </c>
-      <c r="D10" s="7">
+      <c r="C10" s="8">
+        <v>1</v>
+      </c>
+      <c r="D10" s="8">
         <v>1.04</v>
       </c>
     </row>
@@ -1257,13 +1214,13 @@
       <c r="A11" s="2">
         <v>45667</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="8">
         <v>1.0900000000000001</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="8">
         <v>0.9</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="8">
         <v>0.995</v>
       </c>
     </row>
@@ -1271,13 +1228,13 @@
       <c r="A12" s="2">
         <v>45668</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="8">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C12" s="7">
-        <v>1</v>
-      </c>
-      <c r="D12" s="7">
+      <c r="C12" s="8">
+        <v>1</v>
+      </c>
+      <c r="D12" s="8">
         <v>1.05</v>
       </c>
     </row>
@@ -1285,13 +1242,13 @@
       <c r="A13" s="2">
         <v>45669</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="8">
         <v>1.1100000000000001</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="8">
         <v>0.9</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="8">
         <v>1.0049999999999999</v>
       </c>
     </row>
@@ -1299,13 +1256,13 @@
       <c r="A14" s="2">
         <v>45670</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="8">
         <v>1.1200000000000001</v>
       </c>
-      <c r="C14" s="7">
-        <v>1</v>
-      </c>
-      <c r="D14" s="7">
+      <c r="C14" s="8">
+        <v>1</v>
+      </c>
+      <c r="D14" s="8">
         <v>1.06</v>
       </c>
     </row>
@@ -1313,13 +1270,13 @@
       <c r="A15" s="2">
         <v>45671</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="8">
         <v>1.1299999999999999</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="8">
         <v>0.9</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="8">
         <v>1.0149999999999999</v>
       </c>
     </row>
@@ -1327,13 +1284,13 @@
       <c r="A16" s="2">
         <v>45672</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="8">
         <v>1.1399999999999999</v>
       </c>
-      <c r="C16" s="7">
-        <v>1</v>
-      </c>
-      <c r="D16" s="7">
+      <c r="C16" s="8">
+        <v>1</v>
+      </c>
+      <c r="D16" s="8">
         <v>1.07</v>
       </c>
     </row>
@@ -1341,13 +1298,13 @@
       <c r="A17" s="2">
         <v>45673</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="8">
         <v>1.1499999999999999</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="8">
         <v>0.9</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="8">
         <v>1.0249999999999999</v>
       </c>
     </row>
@@ -1355,13 +1312,13 @@
       <c r="A18" s="2">
         <v>45674</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="8">
         <v>1.1599999999999999</v>
       </c>
-      <c r="C18" s="7">
-        <v>1</v>
-      </c>
-      <c r="D18" s="7">
+      <c r="C18" s="8">
+        <v>1</v>
+      </c>
+      <c r="D18" s="8">
         <v>1.08</v>
       </c>
     </row>
@@ -1369,13 +1326,13 @@
       <c r="A19" s="2">
         <v>45675</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="8">
         <v>1.17</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="8">
         <v>0.9</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="8">
         <v>1.0349999999999999</v>
       </c>
     </row>
@@ -1383,13 +1340,13 @@
       <c r="A20" s="2">
         <v>45676</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="8">
         <v>1.18</v>
       </c>
-      <c r="C20" s="7">
-        <v>1</v>
-      </c>
-      <c r="D20" s="7">
+      <c r="C20" s="8">
+        <v>1</v>
+      </c>
+      <c r="D20" s="8">
         <v>1.0900000000000001</v>
       </c>
     </row>
@@ -1397,13 +1354,13 @@
       <c r="A21" s="2">
         <v>45677</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="8">
         <v>1.19</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="8">
         <v>0.9</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="8">
         <v>1.0449999999999999</v>
       </c>
     </row>
@@ -1411,13 +1368,13 @@
       <c r="A22" s="2">
         <v>45678</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="8">
         <v>1.2</v>
       </c>
-      <c r="C22" s="7">
-        <v>1</v>
-      </c>
-      <c r="D22" s="7">
+      <c r="C22" s="8">
+        <v>1</v>
+      </c>
+      <c r="D22" s="8">
         <v>1.1000000000000001</v>
       </c>
     </row>
@@ -1425,13 +1382,13 @@
       <c r="A23" s="2">
         <v>45679</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="8">
         <v>1.21</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="8">
         <v>0.9</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="8">
         <v>1.0549999999999999</v>
       </c>
     </row>
@@ -1439,13 +1396,13 @@
       <c r="A24" s="2">
         <v>45680</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="8">
         <v>1.22</v>
       </c>
-      <c r="C24" s="7">
-        <v>1</v>
-      </c>
-      <c r="D24" s="7">
+      <c r="C24" s="8">
+        <v>1</v>
+      </c>
+      <c r="D24" s="8">
         <v>1.1100000000000001</v>
       </c>
     </row>
@@ -1453,13 +1410,13 @@
       <c r="A25" s="2">
         <v>45681</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="8">
         <v>1.23</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="8">
         <v>0.9</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="8">
         <v>1.0649999999999999</v>
       </c>
     </row>
@@ -1467,13 +1424,13 @@
       <c r="A26" s="2">
         <v>45682</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="8">
         <v>1.24</v>
       </c>
-      <c r="C26" s="7">
-        <v>1</v>
-      </c>
-      <c r="D26" s="7">
+      <c r="C26" s="8">
+        <v>1</v>
+      </c>
+      <c r="D26" s="8">
         <v>1.1200000000000001</v>
       </c>
     </row>
@@ -1481,13 +1438,13 @@
       <c r="A27" s="2">
         <v>45683</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="8">
         <v>1.25</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="8">
         <v>0.9</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="8">
         <v>1.075</v>
       </c>
     </row>
@@ -1495,13 +1452,13 @@
       <c r="A28" s="2">
         <v>45684</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="8">
         <v>1.26</v>
       </c>
-      <c r="C28" s="7">
-        <v>1</v>
-      </c>
-      <c r="D28" s="7">
+      <c r="C28" s="8">
+        <v>1</v>
+      </c>
+      <c r="D28" s="8">
         <v>1.1299999999999999</v>
       </c>
     </row>
@@ -1509,13 +1466,13 @@
       <c r="A29" s="2">
         <v>45685</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="8">
         <v>1.27</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="8">
         <v>0.9</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="8">
         <v>1.085</v>
       </c>
     </row>
@@ -1523,13 +1480,13 @@
       <c r="A30" s="2">
         <v>45686</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="8">
         <v>1.28</v>
       </c>
-      <c r="C30" s="7">
-        <v>1</v>
-      </c>
-      <c r="D30" s="7">
+      <c r="C30" s="8">
+        <v>1</v>
+      </c>
+      <c r="D30" s="8">
         <v>1.1399999999999999</v>
       </c>
     </row>
@@ -1537,13 +1494,13 @@
       <c r="A31" s="2">
         <v>45687</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="8">
         <v>1.29</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="8">
         <v>0.9</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="8">
         <v>1.095</v>
       </c>
     </row>
@@ -1551,13 +1508,13 @@
       <c r="A32" s="2">
         <v>45688</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="8">
         <v>1.3</v>
       </c>
-      <c r="C32" s="7">
-        <v>1</v>
-      </c>
-      <c r="D32" s="7">
+      <c r="C32" s="8">
+        <v>1</v>
+      </c>
+      <c r="D32" s="8">
         <v>1.1499999999999999</v>
       </c>
     </row>
@@ -1565,13 +1522,13 @@
       <c r="A33" s="2">
         <v>45689</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="8">
         <v>1.31</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="8">
         <v>0.9</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="8">
         <v>1.105</v>
       </c>
     </row>
@@ -1626,10 +1583,10 @@
       <c r="A3" s="2">
         <v>45658</v>
       </c>
-      <c r="B3" s="5">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5">
+      <c r="B3" s="6">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
         <v>1</v>
       </c>
       <c r="D3" s="3">
@@ -1643,10 +1600,10 @@
       <c r="A4" s="2">
         <v>45659</v>
       </c>
-      <c r="B4" s="5">
-        <v>1</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="B4" s="6">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6">
         <v>1</v>
       </c>
       <c r="D4" s="3">
@@ -1660,10 +1617,10 @@
       <c r="A5" s="2">
         <v>45660</v>
       </c>
-      <c r="B5" s="5">
-        <v>1</v>
-      </c>
-      <c r="C5" s="5">
+      <c r="B5" s="6">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6">
         <v>1</v>
       </c>
       <c r="D5" s="3">
@@ -1679,10 +1636,10 @@
       <c r="A6" s="2">
         <v>45661</v>
       </c>
-      <c r="B6" s="5">
-        <v>1</v>
-      </c>
-      <c r="C6" s="5">
+      <c r="B6" s="6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6">
         <v>1</v>
       </c>
       <c r="D6" s="3">
@@ -1698,10 +1655,10 @@
       <c r="A7" s="2">
         <v>45662</v>
       </c>
-      <c r="B7" s="5">
-        <v>1</v>
-      </c>
-      <c r="C7" s="5">
+      <c r="B7" s="6">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6">
         <v>1</v>
       </c>
       <c r="D7" s="3">
@@ -1717,10 +1674,10 @@
       <c r="A8" s="2">
         <v>45663</v>
       </c>
-      <c r="B8" s="5">
-        <v>1</v>
-      </c>
-      <c r="C8" s="5">
+      <c r="B8" s="6">
+        <v>1</v>
+      </c>
+      <c r="C8" s="6">
         <v>1</v>
       </c>
       <c r="D8" s="3">
@@ -1736,10 +1693,10 @@
       <c r="A9" s="2">
         <v>45664</v>
       </c>
-      <c r="B9" s="5">
-        <v>1</v>
-      </c>
-      <c r="C9" s="5">
+      <c r="B9" s="6">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6">
         <v>1</v>
       </c>
       <c r="D9" s="3">
@@ -1755,10 +1712,10 @@
       <c r="A10" s="2">
         <v>45665</v>
       </c>
-      <c r="B10" s="5">
-        <v>1</v>
-      </c>
-      <c r="C10" s="5">
+      <c r="B10" s="6">
+        <v>1</v>
+      </c>
+      <c r="C10" s="6">
         <v>1</v>
       </c>
       <c r="D10" s="3">
@@ -1774,10 +1731,10 @@
       <c r="A11" s="2">
         <v>45666</v>
       </c>
-      <c r="B11" s="5">
-        <v>1</v>
-      </c>
-      <c r="C11" s="5">
+      <c r="B11" s="6">
+        <v>1</v>
+      </c>
+      <c r="C11" s="6">
         <v>1</v>
       </c>
       <c r="D11" s="3">
@@ -1793,10 +1750,10 @@
       <c r="A12" s="2">
         <v>45667</v>
       </c>
-      <c r="B12" s="5">
-        <v>1</v>
-      </c>
-      <c r="C12" s="5">
+      <c r="B12" s="6">
+        <v>1</v>
+      </c>
+      <c r="C12" s="6">
         <v>1</v>
       </c>
       <c r="D12" s="3">
@@ -1812,10 +1769,10 @@
       <c r="A13" s="2">
         <v>45668</v>
       </c>
-      <c r="B13" s="5">
-        <v>1</v>
-      </c>
-      <c r="C13" s="5">
+      <c r="B13" s="6">
+        <v>1</v>
+      </c>
+      <c r="C13" s="6">
         <v>1</v>
       </c>
       <c r="D13" s="3">
@@ -1831,10 +1788,10 @@
       <c r="A14" s="2">
         <v>45669</v>
       </c>
-      <c r="B14" s="5">
-        <v>1</v>
-      </c>
-      <c r="C14" s="5">
+      <c r="B14" s="6">
+        <v>1</v>
+      </c>
+      <c r="C14" s="6">
         <v>1</v>
       </c>
       <c r="D14" s="3">
@@ -1850,10 +1807,10 @@
       <c r="A15" s="2">
         <v>45670</v>
       </c>
-      <c r="B15" s="5">
-        <v>1</v>
-      </c>
-      <c r="C15" s="5">
+      <c r="B15" s="6">
+        <v>1</v>
+      </c>
+      <c r="C15" s="6">
         <v>1</v>
       </c>
       <c r="D15" s="3">
@@ -1869,10 +1826,10 @@
       <c r="A16" s="2">
         <v>45671</v>
       </c>
-      <c r="B16" s="5">
-        <v>1</v>
-      </c>
-      <c r="C16" s="5">
+      <c r="B16" s="6">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6">
         <v>1</v>
       </c>
       <c r="D16" s="3">
@@ -1888,10 +1845,10 @@
       <c r="A17" s="2">
         <v>45672</v>
       </c>
-      <c r="B17" s="5">
-        <v>1</v>
-      </c>
-      <c r="C17" s="5">
+      <c r="B17" s="6">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6">
         <v>1</v>
       </c>
       <c r="D17" s="3">
@@ -1907,10 +1864,10 @@
       <c r="A18" s="2">
         <v>45673</v>
       </c>
-      <c r="B18" s="5">
-        <v>1</v>
-      </c>
-      <c r="C18" s="5">
+      <c r="B18" s="6">
+        <v>1</v>
+      </c>
+      <c r="C18" s="6">
         <v>1</v>
       </c>
       <c r="D18" s="3">
@@ -1926,10 +1883,10 @@
       <c r="A19" s="2">
         <v>45674</v>
       </c>
-      <c r="B19" s="5">
-        <v>1</v>
-      </c>
-      <c r="C19" s="5">
+      <c r="B19" s="6">
+        <v>1</v>
+      </c>
+      <c r="C19" s="6">
         <v>1</v>
       </c>
       <c r="D19" s="3">
@@ -1945,10 +1902,10 @@
       <c r="A20" s="2">
         <v>45675</v>
       </c>
-      <c r="B20" s="5">
-        <v>1</v>
-      </c>
-      <c r="C20" s="5">
+      <c r="B20" s="6">
+        <v>1</v>
+      </c>
+      <c r="C20" s="6">
         <v>1</v>
       </c>
       <c r="D20" s="3">
@@ -1964,10 +1921,10 @@
       <c r="A21" s="2">
         <v>45676</v>
       </c>
-      <c r="B21" s="5">
-        <v>1</v>
-      </c>
-      <c r="C21" s="5">
+      <c r="B21" s="6">
+        <v>1</v>
+      </c>
+      <c r="C21" s="6">
         <v>1</v>
       </c>
       <c r="D21" s="3">
@@ -1983,10 +1940,10 @@
       <c r="A22" s="2">
         <v>45677</v>
       </c>
-      <c r="B22" s="5">
-        <v>1</v>
-      </c>
-      <c r="C22" s="5">
+      <c r="B22" s="6">
+        <v>1</v>
+      </c>
+      <c r="C22" s="6">
         <v>1</v>
       </c>
       <c r="D22" s="3">
@@ -2002,10 +1959,10 @@
       <c r="A23" s="2">
         <v>45678</v>
       </c>
-      <c r="B23" s="5">
-        <v>1</v>
-      </c>
-      <c r="C23" s="5">
+      <c r="B23" s="6">
+        <v>1</v>
+      </c>
+      <c r="C23" s="6">
         <v>1</v>
       </c>
       <c r="D23" s="3">
@@ -2021,10 +1978,10 @@
       <c r="A24" s="2">
         <v>45679</v>
       </c>
-      <c r="B24" s="5">
-        <v>1</v>
-      </c>
-      <c r="C24" s="5">
+      <c r="B24" s="6">
+        <v>1</v>
+      </c>
+      <c r="C24" s="6">
         <v>1</v>
       </c>
       <c r="D24" s="3">
@@ -2040,10 +1997,10 @@
       <c r="A25" s="2">
         <v>45680</v>
       </c>
-      <c r="B25" s="5">
-        <v>1</v>
-      </c>
-      <c r="C25" s="5">
+      <c r="B25" s="6">
+        <v>1</v>
+      </c>
+      <c r="C25" s="6">
         <v>1</v>
       </c>
       <c r="D25" s="3">
@@ -2059,10 +2016,10 @@
       <c r="A26" s="2">
         <v>45681</v>
       </c>
-      <c r="B26" s="5">
-        <v>1</v>
-      </c>
-      <c r="C26" s="5">
+      <c r="B26" s="6">
+        <v>1</v>
+      </c>
+      <c r="C26" s="6">
         <v>1</v>
       </c>
       <c r="D26" s="3">
@@ -2078,10 +2035,10 @@
       <c r="A27" s="2">
         <v>45682</v>
       </c>
-      <c r="B27" s="5">
-        <v>1</v>
-      </c>
-      <c r="C27" s="5">
+      <c r="B27" s="6">
+        <v>1</v>
+      </c>
+      <c r="C27" s="6">
         <v>1</v>
       </c>
       <c r="D27" s="3">
@@ -2097,10 +2054,10 @@
       <c r="A28" s="2">
         <v>45683</v>
       </c>
-      <c r="B28" s="5">
-        <v>1</v>
-      </c>
-      <c r="C28" s="5">
+      <c r="B28" s="6">
+        <v>1</v>
+      </c>
+      <c r="C28" s="6">
         <v>1</v>
       </c>
       <c r="D28" s="3">
@@ -2116,10 +2073,10 @@
       <c r="A29" s="2">
         <v>45684</v>
       </c>
-      <c r="B29" s="5">
-        <v>1</v>
-      </c>
-      <c r="C29" s="5">
+      <c r="B29" s="6">
+        <v>1</v>
+      </c>
+      <c r="C29" s="6">
         <v>1</v>
       </c>
       <c r="D29" s="3">
@@ -2135,10 +2092,10 @@
       <c r="A30" s="2">
         <v>45685</v>
       </c>
-      <c r="B30" s="5">
-        <v>1</v>
-      </c>
-      <c r="C30" s="5">
+      <c r="B30" s="6">
+        <v>1</v>
+      </c>
+      <c r="C30" s="6">
         <v>1</v>
       </c>
       <c r="D30" s="3">
@@ -2154,10 +2111,10 @@
       <c r="A31" s="2">
         <v>45686</v>
       </c>
-      <c r="B31" s="5">
-        <v>1</v>
-      </c>
-      <c r="C31" s="5">
+      <c r="B31" s="6">
+        <v>1</v>
+      </c>
+      <c r="C31" s="6">
         <v>1</v>
       </c>
       <c r="D31" s="3">
@@ -2173,10 +2130,10 @@
       <c r="A32" s="2">
         <v>45687</v>
       </c>
-      <c r="B32" s="5">
-        <v>1</v>
-      </c>
-      <c r="C32" s="5">
+      <c r="B32" s="6">
+        <v>1</v>
+      </c>
+      <c r="C32" s="6">
         <v>1</v>
       </c>
       <c r="D32" s="3">
@@ -2192,10 +2149,10 @@
       <c r="A33" s="2">
         <v>45688</v>
       </c>
-      <c r="B33" s="5">
-        <v>1</v>
-      </c>
-      <c r="C33" s="5">
+      <c r="B33" s="6">
+        <v>1</v>
+      </c>
+      <c r="C33" s="6">
         <v>1</v>
       </c>
       <c r="D33" s="3">
@@ -2211,10 +2168,10 @@
       <c r="A34" s="2">
         <v>45689</v>
       </c>
-      <c r="B34" s="5">
-        <v>1</v>
-      </c>
-      <c r="C34" s="5">
+      <c r="B34" s="6">
+        <v>1</v>
+      </c>
+      <c r="C34" s="6">
         <v>1</v>
       </c>
       <c r="D34" s="3">
@@ -2240,13 +2197,13 @@
     <col min="2" max="3" width="10.07421875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.53515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.61328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.23046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.53515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.15234375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.61328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.23046875" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.53515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.15234375" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.61328125" style="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.84375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.07421875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.4609375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.07421875" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.4609375" style="5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="20.07421875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2264,25 +2221,25 @@
       <c r="E1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>30</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="4" t="s">
         <v>33</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -2295,40 +2252,40 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>40877</v>
+        <v>45658</v>
       </c>
       <c r="C2" s="2">
-        <v>46112</v>
+        <v>45689</v>
       </c>
       <c r="D2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="5">
+        <v>31</v>
+      </c>
+      <c r="G2" s="5">
+        <v>2308.36</v>
+      </c>
+      <c r="H2" s="5">
+        <v>2.67</v>
+      </c>
+      <c r="I2" s="5">
+        <v>79.53</v>
+      </c>
+      <c r="J2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="5">
+        <v>0</v>
+      </c>
+      <c r="L2" s="5">
+        <v>0</v>
+      </c>
+      <c r="M2" t="s">
         <v>35</v>
-      </c>
-      <c r="E2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
@@ -2336,40 +2293,40 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>40877</v>
+        <v>45658</v>
       </c>
       <c r="C3" s="2">
-        <v>46112</v>
+        <v>45689</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="5">
+        <v>-10</v>
+      </c>
+      <c r="G3" s="5">
+        <v>-71.099999999999994</v>
+      </c>
+      <c r="H3" s="5">
+        <v>167.17</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0.31</v>
+      </c>
+      <c r="J3">
+        <v>0.47</v>
+      </c>
+      <c r="K3" s="5">
+        <v>-10</v>
+      </c>
+      <c r="L3" s="5">
+        <v>-10</v>
+      </c>
+      <c r="M3" t="s">
         <v>36</v>
-      </c>
-      <c r="F3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K3" t="s">
-        <v>49</v>
-      </c>
-      <c r="L3" t="s">
-        <v>50</v>
-      </c>
-      <c r="M3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
@@ -2377,40 +2334,83 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>40877</v>
+        <v>45658</v>
       </c>
       <c r="C4" s="2">
-        <v>46112</v>
+        <v>45689</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G4" t="s">
-        <v>55</v>
-      </c>
-      <c r="H4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I4" t="s">
-        <v>57</v>
-      </c>
-      <c r="J4" t="s">
-        <v>58</v>
-      </c>
-      <c r="K4" t="s">
-        <v>59</v>
-      </c>
-      <c r="L4" t="s">
-        <v>60</v>
+        <v>37</v>
+      </c>
+      <c r="F4" s="5">
+        <v>10.5</v>
+      </c>
+      <c r="G4" s="5">
+        <v>224.27</v>
+      </c>
+      <c r="H4" s="5">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="J4">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="K4" s="5">
+        <v>-4.5</v>
+      </c>
+      <c r="L4" s="5">
+        <v>-4.17</v>
       </c>
       <c r="M4" t="s">
-        <v>61</v>
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10D26B0-871D-42C0-9F7F-1E045EDA585A}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="68.84375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/public/tests/data/test_simple.xlsx
+++ b/public/tests/data/test_simple.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71227824-674B-4214-980A-60497E825BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30FE0079-4F17-4DA9-9DF3-311306018451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2364,7 +2364,7 @@
         <v>-4.5</v>
       </c>
       <c r="L4" s="5">
-        <v>-4.17</v>
+        <v>-4.1900000000000004</v>
       </c>
       <c r="M4" t="s">
         <v>38</v>

--- a/public/tests/data/test_simple.xlsx
+++ b/public/tests/data/test_simple.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30FE0079-4F17-4DA9-9DF3-311306018451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6646896-9B02-44A9-9632-24DC20A72B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,6 @@
     <sheet name="Expected_Values" sheetId="6" r:id="rId5"/>
     <sheet name="Expected_Weights" sheetId="7" r:id="rId6"/>
     <sheet name="Expected_Stats" sheetId="10" r:id="rId7"/>
-    <sheet name="Sheet7" sheetId="11" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="40">
   <si>
     <t>Name</t>
   </si>
@@ -150,40 +149,19 @@
     <t>Max Drawdown Period</t>
   </si>
   <si>
-    <t>1.15 years</t>
-  </si>
-  <si>
-    <t>1.34 years</t>
-  </si>
-  <si>
     <t>full</t>
   </si>
   <si>
-    <t>1.08 years</t>
-  </si>
-  <si>
     <t>once</t>
   </si>
   <si>
-    <t>$$CAGR = (1.31)^{\frac{365.25}{31}} - 1 \approx 23.0836 \rightarrow 2308.36\%$$</t>
-  </si>
-  <si>
-    <t>Portfolio 1 ($100\%$ A1):</t>
-  </si>
-  <si>
-    <t>Portfolio 2 ($100\%$ A2):</t>
-  </si>
-  <si>
-    <t>$$CAGR = (0.90)^{\frac{365.25}{31}} - 1 \approx -0.7112 \rightarrow -71.1\%$$</t>
-  </si>
-  <si>
-    <t>Portfolio 3 ($50/50$ Drift):</t>
-  </si>
-  <si>
-    <t>$$CAGR = (1.105)^{\frac{365.25}{31}} - 1 \approx 2.2427 \rightarrow 224.27\%$$</t>
-  </si>
-  <si>
     <t>inf</t>
+  </si>
+  <si>
+    <t>0 days</t>
+  </si>
+  <si>
+    <t>1 days</t>
   </si>
 </sst>
 </file>
@@ -2258,10 +2236,10 @@
         <v>45689</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F2" s="5">
         <v>31</v>
@@ -2276,7 +2254,7 @@
         <v>79.53</v>
       </c>
       <c r="J2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="K2" s="5">
         <v>0</v>
@@ -2285,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
@@ -2299,10 +2277,10 @@
         <v>45689</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F3" s="5">
         <v>-10</v>
@@ -2326,7 +2304,7 @@
         <v>-10</v>
       </c>
       <c r="M3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
@@ -2340,10 +2318,10 @@
         <v>45689</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F4" s="5">
         <v>10.5</v>
@@ -2367,50 +2345,7 @@
         <v>-4.1900000000000004</v>
       </c>
       <c r="M4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10D26B0-871D-42C0-9F7F-1E045EDA585A}">
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="68.84375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/public/tests/data/test_simple.xlsx
+++ b/public/tests/data/test_simple.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6646896-9B02-44A9-9632-24DC20A72B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF7A474-E95D-4749-8487-C10811C735FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="38">
   <si>
     <t>Name</t>
   </si>
@@ -87,12 +87,6 @@
   </si>
   <si>
     <t>Portfolios</t>
-  </si>
-  <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>Proxy</t>
   </si>
   <si>
     <t>Date</t>
@@ -577,13 +571,13 @@
         <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
@@ -616,46 +610,34 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C271D88-DDEC-4A65-8905-A99CA73725FC}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="14.921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -673,7 +655,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>10</v>
@@ -1050,16 +1032,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
@@ -1525,24 +1507,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="E1" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>10</v>
@@ -2188,46 +2170,46 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="M1" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="N1" s="1"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2">
         <v>45658</v>
@@ -2236,10 +2218,10 @@
         <v>45689</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F2" s="5">
         <v>31</v>
@@ -2254,7 +2236,7 @@
         <v>79.53</v>
       </c>
       <c r="J2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K2" s="5">
         <v>0</v>
@@ -2263,12 +2245,12 @@
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2">
         <v>45658</v>
@@ -2277,10 +2259,10 @@
         <v>45689</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F3" s="5">
         <v>-10</v>
@@ -2304,12 +2286,12 @@
         <v>-10</v>
       </c>
       <c r="M3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2">
         <v>45658</v>
@@ -2318,10 +2300,10 @@
         <v>45689</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F4" s="5">
         <v>10.5</v>
@@ -2345,7 +2327,7 @@
         <v>-4.1900000000000004</v>
       </c>
       <c r="M4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/public/tests/data/test_simple.xlsx
+++ b/public/tests/data/test_simple.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF7A474-E95D-4749-8487-C10811C735FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B986BBD5-A956-435D-8150-90ED42B7F000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -62,12 +62,6 @@
     <t>end</t>
   </si>
   <si>
-    <t>portfolios_source</t>
-  </si>
-  <si>
-    <t>assets_source</t>
-  </si>
-  <si>
     <t>Assets</t>
   </si>
   <si>
@@ -156,6 +150,12 @@
   </si>
   <si>
     <t>1 days</t>
+  </si>
+  <si>
+    <t>portfolios</t>
+  </si>
+  <si>
+    <t>assets</t>
   </si>
 </sst>
 </file>
@@ -163,7 +163,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -218,8 +218,8 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -504,7 +504,7 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="15.3828125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.84375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.4609375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -542,18 +542,18 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -568,21 +568,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -593,7 +593,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3">
@@ -618,7 +618,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -626,18 +626,18 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
         <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
         <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -655,13 +655,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
@@ -1032,16 +1032,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>16</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
@@ -1507,36 +1507,36 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="E1" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
@@ -2170,46 +2170,46 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="M1" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="N1" s="1"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2">
         <v>45658</v>
@@ -2218,10 +2218,10 @@
         <v>45689</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F2" s="5">
         <v>31</v>
@@ -2236,7 +2236,7 @@
         <v>79.53</v>
       </c>
       <c r="J2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K2" s="5">
         <v>0</v>
@@ -2245,12 +2245,12 @@
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2">
         <v>45658</v>
@@ -2259,10 +2259,10 @@
         <v>45689</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F3" s="5">
         <v>-10</v>
@@ -2286,12 +2286,12 @@
         <v>-10</v>
       </c>
       <c r="M3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2">
         <v>45658</v>
@@ -2300,10 +2300,10 @@
         <v>45689</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F4" s="5">
         <v>10.5</v>
@@ -2327,7 +2327,7 @@
         <v>-4.1900000000000004</v>
       </c>
       <c r="M4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
